--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$11</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$27</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="201">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,25 +76,46 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2609/0105</t>
-  </si>
-  <si>
-    <t>Daily</t>
+    <t>MR2609/0216</t>
+  </si>
+  <si>
+    <t>220KV_Amk-Traction no.2</t>
+  </si>
+  <si>
+    <t>220KV_AMARKANTAK</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>Main Bus 2 jmpher dismantling work</t>
+  </si>
+  <si>
+    <t>15-09-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>15-09-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>Prashant Sharma</t>
+  </si>
+  <si>
+    <t>8989986610</t>
+  </si>
+  <si>
+    <t>MR2609/0220</t>
   </si>
   <si>
     <t>220KV_220KV Main Bus - 02</t>
   </si>
   <si>
-    <t>220KV_AMARKANTAK</t>
-  </si>
-  <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>Dismantling activities of bay 5,6,7,8</t>
-  </si>
-  <si>
-    <t>09-09-2026 09:00:00</t>
+    <t>Dismantling activities</t>
+  </si>
+  <si>
+    <t>15-09-2026 08:00:00</t>
   </si>
   <si>
     <t>15-09-2026 18:00:00</t>
@@ -124,67 +145,133 @@
     <t>Ajay parteti</t>
   </si>
   <si>
-    <t>MR2609/0193</t>
-  </si>
-  <si>
-    <t>400KV_315 MVA X-MER MAKE BHEL</t>
-  </si>
-  <si>
-    <t>400KV_BHOPAL4</t>
-  </si>
-  <si>
-    <t>DIFFERENTIAL RELAY PROBLEM</t>
-  </si>
-  <si>
-    <t>12-09-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>13-09-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>RAJKUMAR GAYAKI</t>
-  </si>
-  <si>
-    <t>9407528876</t>
-  </si>
-  <si>
-    <t>MR2609/0194</t>
-  </si>
-  <si>
-    <t>220KV_100 MVA Transformer</t>
-  </si>
-  <si>
-    <t>220KV_INDORE EAST (BICHOLI)</t>
-  </si>
-  <si>
-    <t>PRV replacement work</t>
-  </si>
-  <si>
-    <t>13-09-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>13-09-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Er. Ajay Kumar Belwanshi</t>
-  </si>
-  <si>
-    <t>9425802934</t>
-  </si>
-  <si>
-    <t>MR2609/0184</t>
-  </si>
-  <si>
-    <t>132KV_132kv half main bus</t>
-  </si>
-  <si>
-    <t>132KV_KYMORE</t>
-  </si>
-  <si>
-    <t>For 132kv Main Bus upgradation work</t>
-  </si>
-  <si>
-    <t>12-09-2026 10:00:00</t>
+    <t>132KV_40 MVA X-MER NO.1 BHEL</t>
+  </si>
+  <si>
+    <t>220KV_BETUL</t>
+  </si>
+  <si>
+    <t>POST MONSOON MAINT. &amp; TESTING WORK</t>
+  </si>
+  <si>
+    <t>VISHAL KUMAR MALVIYA</t>
+  </si>
+  <si>
+    <t>9425804955</t>
+  </si>
+  <si>
+    <t>MR2609/0218</t>
+  </si>
+  <si>
+    <t>MR2609/0207</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Ajaygarh-Chhatarpur ckt. 1 Line</t>
+  </si>
+  <si>
+    <t>220KV_CHATARPUR</t>
+  </si>
+  <si>
+    <t>for dismentlling of ERS and trasfering conductor</t>
+  </si>
+  <si>
+    <t>Pankaj yadav</t>
+  </si>
+  <si>
+    <t>9406713326</t>
+  </si>
+  <si>
+    <t>MR2609/0219</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Nagda â¿¿ Daloda ckt-2nd</t>
+  </si>
+  <si>
+    <t>220KV_DALODA</t>
+  </si>
+  <si>
+    <t>for flash over Disc insulator replacement work</t>
+  </si>
+  <si>
+    <t>15-09-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>Pappu Singh Solanki</t>
+  </si>
+  <si>
+    <t>9425820041</t>
+  </si>
+  <si>
+    <t>MR2609/0210</t>
+  </si>
+  <si>
+    <t>132KV_132kv Garhakota Sagar Line</t>
+  </si>
+  <si>
+    <t>132KV_GARHAKOTA</t>
+  </si>
+  <si>
+    <t>R and Y CT Replesment</t>
+  </si>
+  <si>
+    <t>SK HAJARI</t>
+  </si>
+  <si>
+    <t>9425620010</t>
+  </si>
+  <si>
+    <t>MR2609/0200</t>
+  </si>
+  <si>
+    <t>220KV_220 KV HANDIA- SARNI FDR.</t>
+  </si>
+  <si>
+    <t>220KV_HANDIYA</t>
+  </si>
+  <si>
+    <t>CT Tan Delta &amp; DPR Relay Testing work</t>
+  </si>
+  <si>
+    <t>15-09-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>K.R. Dongre</t>
+  </si>
+  <si>
+    <t>9424430754</t>
+  </si>
+  <si>
+    <t>MR2609/0214</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Itarsi-Pipariya Ckt- I</t>
+  </si>
+  <si>
+    <t>220KV_ITARSI</t>
+  </si>
+  <si>
+    <t>For Broken/Flash over disc replacement work</t>
+  </si>
+  <si>
+    <t>15-09-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Ashutosh Rai</t>
+  </si>
+  <si>
+    <t>9425806902</t>
+  </si>
+  <si>
+    <t>MR2609/0212</t>
+  </si>
+  <si>
+    <t>220KV_160MVA BHEL X-MER</t>
+  </si>
+  <si>
+    <t>400KV_KATNI4</t>
+  </si>
+  <si>
+    <t>FOR SHIFTING OF RTCC PANEL</t>
   </si>
   <si>
     <t>SK chaturvedi</t>
@@ -193,6 +280,162 @@
     <t>9425806938</t>
   </si>
   <si>
+    <t>MR2609/0204</t>
+  </si>
+  <si>
+    <t>132KV_132 KV KATNI (400KV S/S) - SLEEMNABAD LINE</t>
+  </si>
+  <si>
+    <t>Jumper Cone Tightening &amp; Other Line Maintenance Wo</t>
+  </si>
+  <si>
+    <t>MANOJ KUMAR TIWARI</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2609/0211</t>
+  </si>
+  <si>
+    <t>132KV_132/33KV 20MVA GEC X-mer</t>
+  </si>
+  <si>
+    <t>132KV_KATRA</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Oil topping in main conservator tank</t>
+  </si>
+  <si>
+    <t>15-09-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Surendra Singh Baheliya</t>
+  </si>
+  <si>
+    <t>9685298331</t>
+  </si>
+  <si>
+    <t>MR2609/0199</t>
+  </si>
+  <si>
+    <t>220KV_200MVA Transformer (CGL)</t>
+  </si>
+  <si>
+    <t>220KV_NEPANAGAR</t>
+  </si>
+  <si>
+    <t>Post Mansoon Maintanance</t>
+  </si>
+  <si>
+    <t>Mr.M.K.Pawar</t>
+  </si>
+  <si>
+    <t>9425805191</t>
+  </si>
+  <si>
+    <t>MR2609/0202</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA Xmer -I CGL</t>
+  </si>
+  <si>
+    <t>220KV_NIMRANI</t>
+  </si>
+  <si>
+    <t>for defective breaker machanism rectification work</t>
+  </si>
+  <si>
+    <t>16-09-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>pradip patidar</t>
+  </si>
+  <si>
+    <t>9425801217</t>
+  </si>
+  <si>
+    <t>MR2609/0209</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Itarsi No-1</t>
+  </si>
+  <si>
+    <t>220KV_PIPARIYA</t>
+  </si>
+  <si>
+    <t>DPR Relay Testing Work.</t>
+  </si>
+  <si>
+    <t>S.K.Dehariya</t>
+  </si>
+  <si>
+    <t>8319638787</t>
+  </si>
+  <si>
+    <t>MR2609/0205</t>
+  </si>
+  <si>
+    <t>220KV_200 MVA X-MER BBL</t>
+  </si>
+  <si>
+    <t>220KV_RATLAM</t>
+  </si>
+  <si>
+    <t>AIR RELEASE WORK AFTER FIRST CHARGING.</t>
+  </si>
+  <si>
+    <t>15-09-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>15-09-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>NIKHIL DUNGE</t>
+  </si>
+  <si>
+    <t>9425801487</t>
+  </si>
+  <si>
+    <t>MR2609/0206</t>
+  </si>
+  <si>
+    <t>220KV_220KV SIDHI - ANUPPUR LINE</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
+  </si>
+  <si>
+    <t>CT TESTING AND RED HOT POINT ATTENDING WORK</t>
+  </si>
+  <si>
+    <t>15-09-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>VISHAL BALADHARE</t>
+  </si>
+  <si>
+    <t>9425804690</t>
+  </si>
+  <si>
+    <t>MR2609/0215</t>
+  </si>
+  <si>
+    <t>132KV_132kV Sidhi - Madwas RTS Ckt</t>
+  </si>
+  <si>
+    <t>Flash Over Disc Replacement</t>
+  </si>
+  <si>
+    <t>G.L Sahu</t>
+  </si>
+  <si>
+    <t>9425805102</t>
+  </si>
+  <si>
     <t>MR2609/0033</t>
   </si>
   <si>
@@ -208,15 +451,63 @@
     <t>07-09-2026 09:00:00</t>
   </si>
   <si>
-    <t>15-09-2026 17:00:00</t>
-  </si>
-  <si>
     <t>Yogesh Chouhan</t>
   </si>
   <si>
     <t>7587570887</t>
   </si>
   <si>
+    <t>MR2609/0213</t>
+  </si>
+  <si>
+    <t>220KV_220kv Damoh(PGCIL) circuit breaker</t>
+  </si>
+  <si>
+    <t>220KV_TIKAMGARH</t>
+  </si>
+  <si>
+    <t>Load shifting on 220kv bus-coupler</t>
+  </si>
+  <si>
+    <t>Pushpendra Kumar soni</t>
+  </si>
+  <si>
+    <t>9425806398</t>
+  </si>
+  <si>
+    <t>MR2609/0208</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA -2nd  bbl-make Transformer</t>
+  </si>
+  <si>
+    <t>Oil topping</t>
+  </si>
+  <si>
+    <t>9525806398</t>
+  </si>
+  <si>
+    <t>MR2609/0203</t>
+  </si>
+  <si>
+    <t>220KV_160MVA X-MER -I MAKE BHEL</t>
+  </si>
+  <si>
+    <t>400KV_UJJAIN4</t>
+  </si>
+  <si>
+    <t>Post monsoon bay maint.&amp; x-mer testing work</t>
+  </si>
+  <si>
+    <t>15-09-2026 09:30:00</t>
+  </si>
+  <si>
+    <t>MR.Santosh chavrasiya</t>
+  </si>
+  <si>
+    <t>9425804677</t>
+  </si>
+  <si>
     <t>132KV_WAIDHAN</t>
   </si>
   <si>
@@ -241,31 +532,100 @@
     <t>ok</t>
   </si>
   <si>
+    <t>sub ld</t>
+  </si>
+  <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
+    <t>real time, as per load management</t>
+  </si>
+  <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>as opportunity s/d</t>
+  </si>
+  <si>
+    <t>RTS consent required</t>
+  </si>
+  <si>
+    <t>ok, line to be in service through TBC</t>
+  </si>
+  <si>
     <t>deferred by site</t>
   </si>
   <si>
-    <t>ok, after load management</t>
+    <t>ok, no shifting work of this ckt to be done during the s/d period</t>
+  </si>
+  <si>
+    <t>ok, charging permission of Electrical Inspector required while charging the ckt</t>
+  </si>
+  <si>
+    <t>NHPTL-TESTING-@-NHPTL - 400KV at BINA-NHPTL - 400KV</t>
+  </si>
+  <si>
+    <t>220KV-BETUL-PANDURNA-1</t>
+  </si>
+  <si>
+    <t>220KV-MEHGAON-AURIYA-1</t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-MAHALGAON-2</t>
+  </si>
+  <si>
+    <t>220KV-DAMOH-SAGAR-2</t>
+  </si>
+  <si>
+    <t>220KV-SATNA-KOTAR-1</t>
+  </si>
+  <si>
+    <t>220KV-SHUJALPUR-RAJGARH-MP-2</t>
   </si>
   <si>
     <t>132KV-VSTPS-WAIDHAN-1</t>
   </si>
   <si>
-    <t>MP_SLDC</t>
+    <t>15-Sep-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS &amp; FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR REPLACEMENT OF DEFECTIVE DICS INSULATOR STRING AT VARIOUS LOCATIONS </t>
+  </si>
+  <si>
+    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
   </si>
   <si>
     <t>FOR REPLACEMENT OF EXISTING CONDUCTOR TO HTLS CONDUCTOR WORK</t>
   </si>
   <si>
-    <t>13-Sep-2026</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>17:00</t>
+    <t>S/I ,SLDC  MPPTCL JABALPUR</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DTD.15.09.2026</t>
   </si>
 </sst>
 </file>
@@ -276,7 +636,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -289,46 +649,35 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -345,12 +694,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -412,51 +761,12 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -464,28 +774,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -493,71 +817,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -586,10 +859,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>90983</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>605333</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>79535</xdr:rowOff>
+      <xdr:rowOff>3335</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -922,469 +1195,1281 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="6" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="11" style="6" customWidth="1"/>
-    <col min="5" max="5" width="37.42578125" style="30" customWidth="1"/>
-    <col min="6" max="6" width="28" style="30" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="40.7109375" style="30" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="6" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12" style="6" customWidth="1"/>
-    <col min="13" max="13" width="30.7109375" style="30" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="6"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="53" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="50.140625" customWidth="1"/>
+    <col min="9" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="37.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3"/>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:13" ht="43.7" customHeight="1">
+      <c r="A1" s="1"/>
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="5"/>
-    </row>
-    <row r="2" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" spans="1:13" s="13" customFormat="1" ht="42" customHeight="1">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <v>46278</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="1"/>
-    </row>
-    <row r="3" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="20">
+        <v>46280</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="12"/>
+    </row>
+    <row r="3" spans="1:13" s="13" customFormat="1" ht="42" customHeight="1">
+      <c r="A3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" s="13" customFormat="1" ht="42" customHeight="1">
+      <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="5"/>
-      <c r="M4" s="25" t="s">
+      <c r="L4" s="16"/>
+      <c r="M4" s="14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+    <row r="5" spans="1:13" ht="36" customHeight="1">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
-      <c r="B5" s="11">
-        <v>46273.538402777776</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="3">
+        <v>46279.691701388889</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="G5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="H5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="I5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="J5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="K5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="L5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L5" s="14" t="s">
+      <c r="M5" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="36" customHeight="1">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46279.726944444446</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="D6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="36" customHeight="1">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46272.745185185187</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="36" customHeight="1">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46279.693981481483</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="36" customHeight="1">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46279.550034722219</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="36" customHeight="1">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46279.696585648147</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="36" customHeight="1">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46279.628877314812</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="36" customHeight="1">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46279.487407407411</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L12" s="6" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
-        <v>2</v>
-      </c>
-      <c r="B6" s="11">
-        <v>46272.745185185187</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="M12" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="36" customHeight="1">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46279.679502314815</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="36" customHeight="1">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46279.638518518521</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="36" customHeight="1">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46279.505416666667</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="36" customHeight="1">
+      <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46279.636423611111</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="36" customHeight="1">
+      <c r="A17" s="2">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46279.42732638889</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="36" customHeight="1">
+      <c r="A18" s="2">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46279.491099537037</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="36" customHeight="1">
+      <c r="A19" s="2">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46279.610937500001</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="36" customHeight="1">
+      <c r="A20" s="2">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46279.539988425924</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="36" customHeight="1">
+      <c r="A21" s="2">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46279.545173611114</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="36" customHeight="1">
+      <c r="A22" s="2">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3">
+        <v>46279.689826388887</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="36" customHeight="1">
+      <c r="A23" s="2">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46268.535208333335</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="36" customHeight="1">
+      <c r="A24" s="2">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46279.664467592593</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="36" customHeight="1">
+      <c r="A25" s="2">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3">
+        <v>46279.597719907404</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="36" customHeight="1">
+      <c r="A26" s="2">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3">
+        <v>46279.498067129629</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="36" customHeight="1">
+      <c r="A27" s="2">
+        <v>23</v>
+      </c>
+      <c r="B27" s="3">
+        <v>46259.779247685183</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="102">
+      <c r="A28" s="2">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="25.5">
+      <c r="A29" s="2">
+        <v>25</v>
+      </c>
+      <c r="B29" s="3"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="38.25">
+      <c r="A30" s="2">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="102">
+      <c r="A31" s="2">
         <v>27</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="B31" s="3"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="63.75">
+      <c r="A32" s="2">
         <v>28</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="B32" s="3"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="63.75">
+      <c r="A33" s="2">
         <v>29</v>
       </c>
-      <c r="F6" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="25" t="s">
+      <c r="B33" s="3"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="25.5">
+      <c r="A34" s="2">
         <v>30</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="B34" s="3"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="25.5">
+      <c r="A35" s="2">
         <v>31</v>
       </c>
-      <c r="J6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11">
-        <v>46277.647928240738</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K7" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="M7" s="25" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
-        <v>4</v>
-      </c>
-      <c r="B8" s="11">
-        <v>46277.730196759258</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J8" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
-        <v>5</v>
-      </c>
-      <c r="B9" s="16">
-        <v>46276.619733796295</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9" s="26" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
-        <v>6</v>
-      </c>
-      <c r="B10" s="21">
-        <v>46268.535208333335</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="L10" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="M10" s="27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20">
-        <v>7</v>
-      </c>
-      <c r="B11" s="21">
-        <v>46259.779247685183</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="L11" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="M11" s="27" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
-        <v>8</v>
-      </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="24">
-        <v>321045</v>
-      </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="28">
-        <v>132</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="I12" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>78</v>
-      </c>
-      <c r="L12" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="M12" s="31" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20">
-        <v>9</v>
-      </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="29"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="36">
+      <c r="H36" s="10"/>
+      <c r="M36" s="11" t="s">
+        <v>199</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
+    <mergeCell ref="E2:L2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$22</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$29</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="235">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,37 +76,85 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2609/0251</t>
-  </si>
-  <si>
-    <t>220KV_220/132kv 160MVA MAKE - CGL</t>
-  </si>
-  <si>
-    <t>220KV_BARWAHA</t>
+    <t>MR2609/0288</t>
+  </si>
+  <si>
+    <t>132KV_63MVA X-mer BBL-2</t>
+  </si>
+  <si>
+    <t>132KV_ASHTA1</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>NIFPS System shifting work</t>
-  </si>
-  <si>
-    <t>17-09-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>17-09-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Er. Imran Beg</t>
-  </si>
-  <si>
-    <t>9425805200</t>
-  </si>
-  <si>
-    <t>MR2609/0254</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Tikamgrah Chhatarpur</t>
+    <t>post monsoon maintenance &amp; Testingwork</t>
+  </si>
+  <si>
+    <t>18-09-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>18-09-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Akram Khan</t>
+  </si>
+  <si>
+    <t>9425804695</t>
+  </si>
+  <si>
+    <t>MR2609/0280</t>
+  </si>
+  <si>
+    <t>132KV_TRANSFORMER</t>
+  </si>
+  <si>
+    <t>132KV_BETUL1</t>
+  </si>
+  <si>
+    <t>Pre mansoon maintenance &amp;Testing  work</t>
+  </si>
+  <si>
+    <t>18-09-2026 09:30:00</t>
+  </si>
+  <si>
+    <t>VISHAL KUMAR MALVIYA</t>
+  </si>
+  <si>
+    <t>9425804955</t>
+  </si>
+  <si>
+    <t>MR2609/0224</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA X-Mer No 3 BHEL</t>
+  </si>
+  <si>
+    <t>220KV_BHOPAL</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>Post monsoon maintenanc work</t>
+  </si>
+  <si>
+    <t>18-09-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>18-09-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>A. K. Jain</t>
+  </si>
+  <si>
+    <t>9425806899</t>
+  </si>
+  <si>
+    <t>MR2609/0285</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Ajaygarh-Chhatarpur  1 line</t>
   </si>
   <si>
     <t>220KV_CHATARPUR</t>
@@ -115,7 +163,7 @@
     <t>Stringing of line conductor</t>
   </si>
   <si>
-    <t>17-09-2026 08:00:00</t>
+    <t>18-09-2026 08:00:00</t>
   </si>
   <si>
     <t>Pankaj yadav</t>
@@ -124,160 +172,361 @@
     <t>9406713326</t>
   </si>
   <si>
-    <t>MR2609/0258</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Saori 2 Feeder load transfer to Bus Coupler</t>
+    <t>MR2609/0292</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Saori 2 Load Transfer to Bus Coupler for Relay Testing work</t>
   </si>
   <si>
     <t>220KV_CHHINDWARA</t>
   </si>
   <si>
-    <t>DPR Relay Testing Work</t>
-  </si>
-  <si>
-    <t>17-09-2026 14:00:00</t>
+    <t>DPR relay Testing and Setting work</t>
+  </si>
+  <si>
+    <t>18-09-2026 14:00:00</t>
   </si>
   <si>
     <t>Er. Dinesh Pawar</t>
   </si>
   <si>
-    <t>7587951131</t>
-  </si>
-  <si>
-    <t>MR2609/0256</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA bhel-make transformer</t>
-  </si>
-  <si>
-    <t>132KV_DIGODA</t>
-  </si>
-  <si>
-    <t>Oil leakage from top of main tank of transformer</t>
-  </si>
-  <si>
-    <t>17-09-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>17-09-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>Santosh lidhi</t>
-  </si>
-  <si>
-    <t>6268345496</t>
-  </si>
-  <si>
-    <t>MR2609/0259</t>
-  </si>
-  <si>
-    <t>220KV_220KV 160MVA X-MER-II</t>
+    <t>0758795113</t>
+  </si>
+  <si>
+    <t>MR2609/0264</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>220KV_220 kv bicholi CB</t>
+  </si>
+  <si>
+    <t>220KV_DEWAS</t>
+  </si>
+  <si>
+    <t>C.B OVERHOLING WORK FROM CO. ENGINEER</t>
+  </si>
+  <si>
+    <t>26-09-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>A.K. JOSHI</t>
+  </si>
+  <si>
+    <t>9424887657</t>
+  </si>
+  <si>
+    <t>MR2609/0261</t>
+  </si>
+  <si>
+    <t>132KV_DEWAS- BAROTHA LINE</t>
+  </si>
+  <si>
+    <t>JUMPER CONE TIGHTING  &amp; OTHER MAINTENANCE WORK.</t>
+  </si>
+  <si>
+    <t>RAVINDRA PATIL</t>
+  </si>
+  <si>
+    <t>8305612190</t>
+  </si>
+  <si>
+    <t>MR2609/0274</t>
+  </si>
+  <si>
+    <t>132KV_132KV Bus -Coupler</t>
+  </si>
+  <si>
+    <t>132KV_DINDORI</t>
+  </si>
+  <si>
+    <t>R-Y-B phase CT replacement work</t>
+  </si>
+  <si>
+    <t>Vikram Singh</t>
+  </si>
+  <si>
+    <t>8319555199</t>
+  </si>
+  <si>
+    <t>MR2609/0283</t>
+  </si>
+  <si>
+    <t>220KV_220 KV 160 MVA XMER II</t>
   </si>
   <si>
     <t>220KV_GWALIOR-II</t>
   </si>
   <si>
-    <t>TRANSFORMER PAINTING</t>
-  </si>
-  <si>
-    <t>17-09-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>17-09-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>RC ARORA</t>
+    <t>XMER PAINTING</t>
+  </si>
+  <si>
+    <t>R C ARORA</t>
   </si>
   <si>
     <t>9425805108</t>
   </si>
   <si>
-    <t>MR2609/0255</t>
-  </si>
-  <si>
-    <t>132KV_132KV IC NO-1 LINE</t>
-  </si>
-  <si>
-    <t>400KV_KATNI4</t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF R,Y,B PHASE CT (400A to 1200A)</t>
-  </si>
-  <si>
-    <t>S K CHATURVEDI</t>
-  </si>
-  <si>
-    <t>9425806938</t>
-  </si>
-  <si>
-    <t>220KV_220 KV BHOPAL FEEDER</t>
-  </si>
-  <si>
-    <t>220KV_MANDIDEEP</t>
-  </si>
-  <si>
-    <t>B-PHASE ct OIL LEAKAGE</t>
-  </si>
-  <si>
-    <t>A.K. VERMA</t>
-  </si>
-  <si>
-    <t>9425801324</t>
-  </si>
-  <si>
-    <t>MR2609/0253</t>
-  </si>
-  <si>
-    <t>MR2609/0237</t>
-  </si>
-  <si>
-    <t>220KV_220KV Sabalgarh Ckt</t>
-  </si>
-  <si>
-    <t>220KV_MORENA</t>
-  </si>
-  <si>
-    <t>220KV CTs Tan Delta Testing</t>
-  </si>
-  <si>
-    <t>17-09-2026 13:00:00</t>
-  </si>
-  <si>
-    <t>Amit Kumar Dhaneliya</t>
-  </si>
-  <si>
-    <t>8370093158</t>
-  </si>
-  <si>
-    <t>MR2609/0238</t>
-  </si>
-  <si>
-    <t>220KV_220KV Adani</t>
-  </si>
-  <si>
-    <t>17-09-2026 16:00:00</t>
-  </si>
-  <si>
-    <t>MR2609/0239</t>
-  </si>
-  <si>
-    <t>220KV_220KV Bus Coupler</t>
-  </si>
-  <si>
-    <t>MR2609/0257</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Tikamgrah Budhera 2</t>
-  </si>
-  <si>
-    <t>220KV_TIKAMGARH</t>
-  </si>
-  <si>
-    <t>For replacement of FO disc insulator</t>
-  </si>
-  <si>
-    <t>Continuous</t>
+    <t>220KV_220KV JAORA NAGARA LINE</t>
+  </si>
+  <si>
+    <t>220KV_JAORA</t>
+  </si>
+  <si>
+    <t>POST MANSONE</t>
+  </si>
+  <si>
+    <t>RAKESH BADGOTYA</t>
+  </si>
+  <si>
+    <t>8305447051</t>
+  </si>
+  <si>
+    <t>MR2609/0268</t>
+  </si>
+  <si>
+    <t>MR2609/0265</t>
+  </si>
+  <si>
+    <t>132KV_132 kv main bus at 400 KV JULWANIYA</t>
+  </si>
+  <si>
+    <t>400KV_JULWANIYA4</t>
+  </si>
+  <si>
+    <t>connecting of jumper on 132 main bus</t>
+  </si>
+  <si>
+    <t>C H Namdev</t>
+  </si>
+  <si>
+    <t>9425802377</t>
+  </si>
+  <si>
+    <t>MR2609/0278</t>
+  </si>
+  <si>
+    <t>132KV_Shutdown on 132KV KATNI I/C NO. 2 Feeder, at 132 kv s/s Katni.</t>
+  </si>
+  <si>
+    <t>132KV_KATNI</t>
+  </si>
+  <si>
+    <t>CT Replacement work</t>
+  </si>
+  <si>
+    <t>R P Rawat</t>
+  </si>
+  <si>
+    <t>9907030507</t>
+  </si>
+  <si>
+    <t>220KV_(1)	220kV Incommer-1 (315MVA ICT-1</t>
+  </si>
+  <si>
+    <t>400KV_MANDSOUR4</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>For carrying out all 220kV Incomer dropper jumper</t>
+  </si>
+  <si>
+    <t>18-09-2026 10:30:00</t>
+  </si>
+  <si>
+    <t>18-09-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>C.P DHAKAD</t>
+  </si>
+  <si>
+    <t>7587951067</t>
+  </si>
+  <si>
+    <t>MR2609/0287</t>
+  </si>
+  <si>
+    <t>MR2609/0273</t>
+  </si>
+  <si>
+    <t>220KV_220KV Bus-Coupler</t>
+  </si>
+  <si>
+    <t>220KV_NEEMUCH</t>
+  </si>
+  <si>
+    <t>safety purpose for CT replacement work</t>
+  </si>
+  <si>
+    <t>S.H. Mansuri</t>
+  </si>
+  <si>
+    <t>7587951068</t>
+  </si>
+  <si>
+    <t>MR2609/0271</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch- Mandsaur-I</t>
+  </si>
+  <si>
+    <t>220KV R&amp;B CT replacement work at 220KV S/s Neemuch</t>
+  </si>
+  <si>
+    <t>MR2609/0279</t>
+  </si>
+  <si>
+    <t>220KV_200 MVA-I (CGPOWOR)</t>
+  </si>
+  <si>
+    <t>220KV_PITHAMPUR (SEC-III)</t>
+  </si>
+  <si>
+    <t>POST MONSOON MAINT WORK</t>
+  </si>
+  <si>
+    <t>RAJU DAS BAIRAGI</t>
+  </si>
+  <si>
+    <t>9425801532</t>
+  </si>
+  <si>
+    <t>MR2609/0260</t>
+  </si>
+  <si>
+    <t>220KV_220kv Sabalgarh Sheopur Ckt -1</t>
+  </si>
+  <si>
+    <t>220KV_SABALGARH</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Suraj Pawar</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>MR2609/0291</t>
+  </si>
+  <si>
+    <t>132KV_50 MVA BBL X-MER</t>
+  </si>
+  <si>
+    <t>132KV_SAGAR1</t>
+  </si>
+  <si>
+    <t>POST MANSOON MAINTINANCE</t>
+  </si>
+  <si>
+    <t>SK HAJARI</t>
+  </si>
+  <si>
+    <t>9425620010</t>
+  </si>
+  <si>
+    <t>MR2609/0270</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Maihar â¿¿ Kymore Ckt-II.</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>,for Bird Guard Installation and line maintenance</t>
+  </si>
+  <si>
+    <t>18-09-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>18-09-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>Mr. R.K. Prajapati</t>
+  </si>
+  <si>
+    <t>9407070182</t>
+  </si>
+  <si>
+    <t>MR2609/0281</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA transformer no . 1ST EMCO</t>
+  </si>
+  <si>
+    <t>220KV_SHIVPURI</t>
+  </si>
+  <si>
+    <t>160 MVA transformer no . 1ST EMCO from 08:00 hrs.</t>
+  </si>
+  <si>
+    <t>DHIRENDRA CHAURASIYA</t>
+  </si>
+  <si>
+    <t>9425805725</t>
+  </si>
+  <si>
+    <t>MR2609/0275</t>
+  </si>
+  <si>
+    <t>400KV_Interconnecting Transformer 315 MVA, 400KV / 220 KV</t>
+  </si>
+  <si>
+    <t>400KV_SINGHAJI TPS</t>
+  </si>
+  <si>
+    <t>Overhauling work</t>
+  </si>
+  <si>
+    <t>25-09-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>YOGESH CHOUHAN</t>
+  </si>
+  <si>
+    <t>7587570887</t>
+  </si>
+  <si>
+    <t>MR2609/0277</t>
+  </si>
+  <si>
+    <t>132KV_63MVAX-MER-1</t>
+  </si>
+  <si>
+    <t>132KV_SIRONJ</t>
+  </si>
+  <si>
+    <t>POST MANSOON MAITANSE</t>
+  </si>
+  <si>
+    <t>132KV S/S SIRONJ</t>
+  </si>
+  <si>
+    <t>9425804982</t>
+  </si>
+  <si>
+    <t>MR2609/0294</t>
+  </si>
+  <si>
+    <t>132KV_132 kv vinoba bhave- VFJ line</t>
+  </si>
+  <si>
+    <t>132KV_VINOBA BHAVE</t>
+  </si>
+  <si>
+    <t>For extension work of 132 kv yard</t>
+  </si>
+  <si>
+    <t>MR. ASHOK BINGHADE</t>
+  </si>
+  <si>
+    <t>7509148945</t>
   </si>
   <si>
     <t>132KV_WAIDHAN</t>
@@ -304,10 +553,46 @@
     <t>DHARMENDRA  DWIVEDI</t>
   </si>
   <si>
+    <t>MR2609/0282</t>
+  </si>
+  <si>
+    <t>132KV_50_MVA_BBL_2</t>
+  </si>
+  <si>
+    <t>132KV_WARASEONI</t>
+  </si>
+  <si>
+    <t>33kV I/C-II VCB machanism problem attending work</t>
+  </si>
+  <si>
+    <t>18-09-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>18-09-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>Sandeep Damahe</t>
+  </si>
+  <si>
+    <t>9425805009</t>
+  </si>
+  <si>
+    <t>sub ld</t>
+  </si>
+  <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>ok, line to be in service through TBC</t>
+    <t>ok, Charging approval required from Electrical Inspector while charging</t>
+  </si>
+  <si>
+    <t>ok, line to be on service through TBC</t>
+  </si>
+  <si>
+    <t>ok, line to be on service through TBC, through sub ld</t>
+  </si>
+  <si>
+    <t>ok</t>
   </si>
   <si>
     <t>real time</t>
@@ -316,64 +601,134 @@
     <t>deferred by site</t>
   </si>
   <si>
-    <t>deferred, not in WR list</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>ok, o&amp;m shall be informed</t>
-  </si>
-  <si>
-    <t>ok, Charging permission of Electrical Inspector required while charging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shall be reviewed in real time due to high loading </t>
-  </si>
-  <si>
-    <t>400KV-NAGDA-SHUJALPUR-2</t>
-  </si>
-  <si>
-    <t>400KV-SINGAJI-PITHAMPUR-1</t>
-  </si>
-  <si>
-    <t>400KV-SINGAJI-PITHAMPUR-2</t>
-  </si>
-  <si>
-    <t>132KV-VSTPS-WAIDHAN-2</t>
-  </si>
-  <si>
-    <t>POWERGRID-WR2 (PGCIL)</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH,NTPC</t>
-  </si>
-  <si>
-    <t>Attending S/D nature defect in line, Non auto mode of ckt 1 is required . Dia to be kept open at both ends.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOWER STRENGHTING WORK AT VARIOUS LOCATIONS </t>
-  </si>
-  <si>
-    <t>FOR REPLACEMENT OF EXISTING CONDUCTOR TO HTLS CONDUCTOR WORK</t>
-  </si>
-  <si>
-    <t>under review</t>
+    <t>ok, load shall be managed/monitored by sub Ld indore</t>
+  </si>
+  <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on mahalgaon bus</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 18.09.2026</t>
+  </si>
+  <si>
+    <t>132 KV SATNA PAWAI LINE SHIFT ON BC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   18.09.2026 11:00:00</t>
+  </si>
+  <si>
+    <t>18.09.2026 18:00:00</t>
+  </si>
+  <si>
+    <t>DEFFERED , NOT IN PORTAL</t>
+  </si>
+  <si>
+    <t>50 MVA X-MER AT 132 KV BILLOWA</t>
+  </si>
+  <si>
+    <t>18.09.2026 11:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.09.2025 13:00:00 </t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>160 MVA X-MER AT 220 KV JABALPUR</t>
+  </si>
+  <si>
+    <t>18.09.2026   09:30:00</t>
+  </si>
+  <si>
+    <t>18.09.2026 17:00:00</t>
+  </si>
+  <si>
+    <t>LOAD SHIFT ON BUS COUPLER</t>
+  </si>
+  <si>
+    <t>DE AIRING WORK</t>
+  </si>
+  <si>
+    <t>NIFPS OIL LEAKAGE ATTEND WORK</t>
+  </si>
+  <si>
+    <t>220KV-PITHAMPUR-RAJGARH-1</t>
+  </si>
+  <si>
+    <t>18-Sep-2026</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>27-Sep-2026</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOR MOD. SHIFTING WORK OF LINE DUE TO CONSTRUTION OF NEW RAILWAY LINE BETWEEN TIRLA- AMJHERA-SARDARPUR SECTION BY WR RATLAM </t>
+  </si>
+  <si>
+    <t>ok, through sub ld, FTC procedure to be followed.</t>
+  </si>
+  <si>
+    <t>220KV-RAJGARH-DHAR-1</t>
+  </si>
+  <si>
+    <t>400KV-SATPURA-ITARSI-1</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhauling work of CB (External agency involved)
+</t>
+  </si>
+  <si>
+    <t>400KV-KIRNAPUR-BHILAI-1</t>
   </si>
   <si>
     <t>09:00</t>
   </si>
   <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
+    <t>FOR PROVIDING VIBRATION DAMPER AT VARIOUS LOCATIONS</t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-GWALIOR-II-1</t>
   </si>
   <si>
     <t>17:00</t>
+  </si>
+  <si>
+    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>220KV-INDORE-UJJAIN-2</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS &amp; FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>SEONI-PG - 220KV - TRANSFER BUS 1</t>
+  </si>
+  <si>
+    <t>20-Sep-2026</t>
+  </si>
+  <si>
+    <t>CB DRIVE OVERHAUL works at Seoni</t>
+  </si>
+  <si>
+    <t>S/I SLDC JABALPUR</t>
+  </si>
+  <si>
+    <t>WR</t>
   </si>
 </sst>
 </file>
@@ -384,7 +739,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -418,13 +773,28 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -444,12 +814,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -541,20 +917,29 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color rgb="FF000000"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -603,28 +988,50 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="5" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -990,20 +1397,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="54.28515625" style="12" customWidth="1"/>
     <col min="6" max="6" width="21.85546875" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="46.85546875" customWidth="1"/>
-    <col min="9" max="10" width="19.42578125" customWidth="1"/>
-    <col min="11" max="11" width="24.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="58.140625" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.5703125" customWidth="1"/>
+    <col min="11" max="11" width="25.140625" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="49.42578125" style="12" customWidth="1"/>
+    <col min="13" max="13" width="45.7109375" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
@@ -1028,17 +1436,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+      <c r="E2" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="20"/>
       <c r="L2" s="1"/>
       <c r="M2" s="9"/>
     </row>
@@ -1104,12 +1514,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46281.580381944441</v>
+        <v>46282.644212962965</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
@@ -1140,22 +1550,21 @@
         <v>25</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46281.61550925926</v>
+        <v>46282.575254629628</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="11" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1180,16 +1589,15 @@
         <v>32</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A22" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46281.68141203704</v>
+        <v>46280.518333333333</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>33</v>
@@ -1202,93 +1610,91 @@
         <v>35</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46281.636458333334</v>
+        <v>46282.6096875</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46281.695208333331</v>
+        <v>46282.686956018515</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>53</v>
@@ -1300,118 +1706,117 @@
         <v>55</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46281.619652777779</v>
+        <v>46282.456365740742</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="E10" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5">
+        <v>46281.73537037037</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="5">
-        <v>46281.594270833331</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46280.620937500003</v>
+        <v>46282.514097222222</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>73</v>
@@ -1420,16 +1825,15 @@
         <v>74</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46280.62222222222</v>
+        <v>46282.60527777778</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>75</v>
@@ -1439,308 +1843,1022 @@
         <v>76</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>77</v>
+        <v>39</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46280.625462962962</v>
+        <v>46282.495821759258</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46281.655104166668</v>
+        <v>46282.459270833337</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46259.788923611108</v>
+        <v>46282.56181712963</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>84</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="D16" s="4"/>
       <c r="E16" s="11" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="M16" s="18" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46281.655104166668</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21" t="s">
+        <v>46282.641759259262</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="I17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="G17" s="20"/>
-      <c r="H17" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="K17" s="22"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M17" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46281.655104166668</v>
-      </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="G18" s="20"/>
-      <c r="H18" s="21" t="s">
+        <v>46282.508587962962</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="I18" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="25">
-        <v>46295.75</v>
-      </c>
-      <c r="K18" s="22"/>
-      <c r="L18" s="23"/>
-      <c r="M18" s="24" t="s">
+      <c r="G18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K18" s="7" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46281.655104166668</v>
-      </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="G19" s="20"/>
-      <c r="H19" s="21" t="s">
+        <v>46282.506932870368</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="I19" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="J19" s="25">
-        <v>46295.75</v>
-      </c>
-      <c r="K19" s="22"/>
-      <c r="L19" s="23"/>
-      <c r="M19" s="24" t="s">
+      <c r="G19" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L19" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46281.655104166668</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="K20" s="22"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="4"/>
+        <v>46282.571458333332</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46281.69971064815</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="D21" s="4"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="19"/>
-    </row>
-    <row r="22" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="4"/>
+      <c r="E21" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46282.656643518516</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="D22" s="4"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="11"/>
+      <c r="E22" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46282.499108796299</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46282.584537037037</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5">
+        <v>46282.525138888886</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46282.561562499999</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46282.689756944441</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46259.788923611108</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>25</v>
+      </c>
+      <c r="B29" s="22">
+        <v>46282.58666666667</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D29" s="21"/>
+      <c r="E29" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="I29" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="J29" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="K29" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="L29" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>26</v>
+      </c>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29" t="s">
+        <v>207</v>
+      </c>
+      <c r="I30" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>27</v>
+      </c>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="I31" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="28" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>28</v>
+      </c>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="I32" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="J32" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="28" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>29</v>
+      </c>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G33" s="31"/>
+      <c r="H33" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="I33" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="J33" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K33" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="L33" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="M33" s="31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>30</v>
+      </c>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="F34" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G34" s="31"/>
+      <c r="H34" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="I34" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="J34" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K34" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="L34" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="M34" s="31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>31</v>
+      </c>
+      <c r="B35" s="31"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="F35" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G35" s="31"/>
+      <c r="H35" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="I35" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="J35" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="K35" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="L35" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="M35" s="31" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>32</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="F36" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G36" s="31"/>
+      <c r="H36" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="I36" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="J36" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="K36" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="L36" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="M36" s="31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>33</v>
+      </c>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="F37" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G37" s="31"/>
+      <c r="H37" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="I37" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="J37" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="K37" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="L37" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="M37" s="31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>34</v>
+      </c>
+      <c r="B38" s="31"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="30" t="s">
+        <v>227</v>
+      </c>
+      <c r="F38" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G38" s="31"/>
+      <c r="H38" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="I38" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="J38" s="30" t="s">
+        <v>228</v>
+      </c>
+      <c r="K38" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="L38" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="M38" s="31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>35</v>
+      </c>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" s="31" t="s">
+        <v>234</v>
+      </c>
+      <c r="G39" s="31"/>
+      <c r="H39" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="I39" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="J39" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="K39" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="L39" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="M39" s="31" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="31"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="33" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="31"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="31"/>
+      <c r="M41" s="32"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="31"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
+    <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="287">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,189 +76,153 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2609/0517</t>
-  </si>
-  <si>
-    <t>132KV_132KV Anuppur-Dongarital ckt</t>
-  </si>
-  <si>
-    <t>220KV_ANUPPUR</t>
+    <t>MR2609/0602</t>
+  </si>
+  <si>
+    <t>132KV_132 KV ASHTA ARNIYAKALA CKT-2</t>
+  </si>
+  <si>
+    <t>400KV_ASHTA4</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
-    <t>For flash over disc replacement &amp; other line work</t>
-  </si>
-  <si>
-    <t>29-09-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>29-09-2026 14:00:00</t>
-  </si>
-  <si>
-    <t>Jagdish Prasad Ashati</t>
-  </si>
-  <si>
-    <t>9424445533</t>
-  </si>
-  <si>
-    <t>MR2609/0519</t>
-  </si>
-  <si>
-    <t>132KV_132KV Anuppur-Janakpur ckt</t>
-  </si>
-  <si>
-    <t>for flash over disc replacement &amp; other line work</t>
-  </si>
-  <si>
-    <t>29-09-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>29-09-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>9224445533</t>
-  </si>
-  <si>
-    <t>MR2609/0534</t>
-  </si>
-  <si>
-    <t>220KV_220 KV ASHTA-SHAJAPUR CKT-2</t>
-  </si>
-  <si>
-    <t>400KV_ASHTA4</t>
-  </si>
-  <si>
     <t>LINE MAINTENANCE WORK</t>
   </si>
   <si>
+    <t>30-09-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>30-09-2026 18:00:00</t>
+  </si>
+  <si>
     <t>NITIN RESHWAL</t>
   </si>
   <si>
     <t>9425804890</t>
   </si>
   <si>
-    <t>MR2609/0368</t>
-  </si>
-  <si>
-    <t>400KV_400KV MAIN BUS -1</t>
-  </si>
-  <si>
-    <t>400KV_BADNAWAR</t>
-  </si>
-  <si>
-    <t>MAIN BUS -1 MAINTENANCE WORK</t>
-  </si>
-  <si>
-    <t>29-09-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>SUNIL BAMNIYA</t>
-  </si>
-  <si>
-    <t>8349013626</t>
-  </si>
-  <si>
-    <t>MR2609/0562</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Bus coupler bay</t>
-  </si>
-  <si>
-    <t>132KV_BALAGHAT</t>
-  </si>
-  <si>
-    <t>132 KV  Bus-Coupler  bay  for Aux. Isolator Replac</t>
-  </si>
-  <si>
-    <t>29-09-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>Sandeep Damahe</t>
-  </si>
-  <si>
-    <t>9425805009</t>
-  </si>
-  <si>
-    <t>MR2609/0535</t>
-  </si>
-  <si>
-    <t>132KV_50MVA X_MER BBL</t>
-  </si>
-  <si>
-    <t>132KV_BATIYAGARH</t>
-  </si>
-  <si>
-    <t>postmansoon maintinance &amp; testing work</t>
-  </si>
-  <si>
-    <t>29-09-2026 11:00:00</t>
-  </si>
-  <si>
-    <t>29-09-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>B.K. Sahu</t>
-  </si>
-  <si>
-    <t>9425801433</t>
-  </si>
-  <si>
-    <t>MR2609/0533</t>
-  </si>
-  <si>
-    <t>132KV_132kV Bhopal Amarawat line of Auxiliary Isolator</t>
+    <t>MR2609/0571</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Bargi- Lakhnadaun</t>
+  </si>
+  <si>
+    <t>132KV_BARGI</t>
+  </si>
+  <si>
+    <t>More than 35 year string replaced through contract</t>
+  </si>
+  <si>
+    <t>30-09-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>06-10-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Jitendra Tiwari</t>
+  </si>
+  <si>
+    <t>9425805298</t>
+  </si>
+  <si>
+    <t>MR2609/0596</t>
+  </si>
+  <si>
+    <t>220KV_220/132KV 160MVA X-MER (BBL)</t>
+  </si>
+  <si>
+    <t>220KV_BARWAHA</t>
+  </si>
+  <si>
+    <t>safety purpose</t>
+  </si>
+  <si>
+    <t>30-09-2026 07:30:00</t>
+  </si>
+  <si>
+    <t>Er. Imran Beg</t>
+  </si>
+  <si>
+    <t>9425805200</t>
+  </si>
+  <si>
+    <t>MR2609/0597</t>
+  </si>
+  <si>
+    <t>220KV_220/132KV 200MVA X-MER (CGL)</t>
+  </si>
+  <si>
+    <t>30-09-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>MR2609/0555</t>
+  </si>
+  <si>
+    <t>132KV_132kV Bhopal amarawat line &amp; Aux. Bus</t>
   </si>
   <si>
     <t>220KV_BHOPAL</t>
   </si>
   <si>
-    <t>Replacement of Auxillary Isolator</t>
+    <t>Conductor change fromTakeoff gantry to line Gantry</t>
+  </si>
+  <si>
+    <t>30-09-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>A.K. Jain</t>
+  </si>
+  <si>
+    <t>9425806899</t>
+  </si>
+  <si>
+    <t>MR2609/0595</t>
+  </si>
+  <si>
+    <t>220KV_220 KV 160 MVA X-Mer No 1 CGL</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>Post monsoon Maintenance work</t>
+  </si>
+  <si>
+    <t>30-09-2026 09:00:00</t>
   </si>
   <si>
     <t>A. K. Jain</t>
   </si>
   <si>
-    <t>9425806899</t>
-  </si>
-  <si>
-    <t>MR2609/0541</t>
-  </si>
-  <si>
-    <t>132KV_132 KV Chhatarpur-Khajuraho Ckt. IInd line</t>
+    <t>MR2609/0551</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Ajaygarh-Chhatarpur Ckt. I line</t>
   </si>
   <si>
     <t>220KV_CHATARPUR</t>
   </si>
   <si>
-    <t>for Dismantling of ERS work</t>
+    <t>Live Line OPGW Installation Work</t>
   </si>
   <si>
     <t>29-09-2026 07:00:00</t>
   </si>
   <si>
+    <t>07-10-2026 19:00:00</t>
+  </si>
+  <si>
     <t>Pankaj yadav</t>
   </si>
   <si>
     <t>9406713326</t>
   </si>
   <si>
-    <t>MR2609/0551</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Ajaygarh-Chhatarpur Ckt. I line</t>
-  </si>
-  <si>
-    <t>Live Line OPGW Installation Work</t>
-  </si>
-  <si>
-    <t>07-10-2026 19:00:00</t>
-  </si>
-  <si>
     <t>MR2609/0553</t>
   </si>
   <si>
@@ -271,16 +235,28 @@
     <t>220KV_220 kV Ajaygarh-Chhatarpur Ckt. II line</t>
   </si>
   <si>
-    <t>MR2609/0549</t>
-  </si>
-  <si>
-    <t>132KV_132KV_ CHHINDWARA SAORI CKT.II</t>
+    <t>MR2609/0601</t>
+  </si>
+  <si>
+    <t>132KV_132 kv chhatarpur Khajuraho -2</t>
+  </si>
+  <si>
+    <t>SD for Dismantling of ERS work at locations No. 10</t>
+  </si>
+  <si>
+    <t>30-09-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>MR2609/0581</t>
+  </si>
+  <si>
+    <t>40MVA_132/33KV_BBL_X'mer_2</t>
   </si>
   <si>
     <t>220KV_CHHINDWARA</t>
   </si>
   <si>
-    <t>for line and Aux. Isolator replacement  work</t>
+    <t>Post Monsoon Maintenance and Testing work</t>
   </si>
   <si>
     <t>Er. Dinesh Pawar</t>
@@ -289,16 +265,73 @@
     <t>7587951131</t>
   </si>
   <si>
-    <t>MR2609/0554</t>
-  </si>
-  <si>
-    <t>132KV_50 MVA XMER</t>
+    <t>MR2609/0587</t>
+  </si>
+  <si>
+    <t>220KV_220 KV Chhindwara Betul Feeder load transfer on Bus-Coupler Code is required  for DPR Relay Testing work</t>
+  </si>
+  <si>
+    <t>DPR Relay Testing work</t>
+  </si>
+  <si>
+    <t>30-09-2026 11:00:00</t>
+  </si>
+  <si>
+    <t>MR2609/0440</t>
+  </si>
+  <si>
+    <t>220KV_220KV PGCIL (Damoh-Damoh) ckt-3</t>
+  </si>
+  <si>
+    <t>220KV_DAMOH</t>
+  </si>
+  <si>
+    <t>Bay Maintenance &amp; Relay Replacement work</t>
+  </si>
+  <si>
+    <t>M.K.Choubey</t>
+  </si>
+  <si>
+    <t>9425801424</t>
+  </si>
+  <si>
+    <t>MR2609/0592</t>
+  </si>
+  <si>
+    <t>132KV_132/33KV 50MVA X-MER   BBL</t>
+  </si>
+  <si>
+    <t>Post Monsoon Maintenance &amp; Testing work</t>
+  </si>
+  <si>
+    <t>MR2609/0577</t>
+  </si>
+  <si>
+    <t>132KV_132/33KV 40MVA T&amp;R X-MER</t>
+  </si>
+  <si>
+    <t>132KV_DEOSAR</t>
+  </si>
+  <si>
+    <t>FOR 33KV RYB PHASE CT REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>RAMESK KUMAR SHAHU</t>
+  </si>
+  <si>
+    <t>8109414234</t>
+  </si>
+  <si>
+    <t>MR2609/0593</t>
+  </si>
+  <si>
+    <t>132KV_50MVA XMER</t>
   </si>
   <si>
     <t>132KV_ESAGARH</t>
   </si>
   <si>
-    <t>PAINTING WORK OF 50MVA XMER</t>
+    <t>PAINTING WORK ON XMER</t>
   </si>
   <si>
     <t>RAKESH SUMAN</t>
@@ -307,34 +340,55 @@
     <t>7587951093</t>
   </si>
   <si>
-    <t>MR2609/0537</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Jabalpur- Birsinghpur ckt-I</t>
-  </si>
-  <si>
-    <t>220KV_JABALPUR</t>
-  </si>
-  <si>
-    <t>Disc F/o change at loc. 197  Top, Middle Ph</t>
-  </si>
-  <si>
-    <t>29-09-2026 12:00:00</t>
-  </si>
-  <si>
-    <t>Jitendra Tiwari</t>
-  </si>
-  <si>
-    <t>9425805298</t>
-  </si>
-  <si>
-    <t>MR2609/0539</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Jabalpur- Birsinghpur ckt-II</t>
-  </si>
-  <si>
-    <t>29-09-2026 13:00:00</t>
+    <t>MR2609/0575</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Gorabazar- Amarkantak</t>
+  </si>
+  <si>
+    <t>220KV_GORABAZAR</t>
+  </si>
+  <si>
+    <t>Disc Change at loc. 349 Top Ph</t>
+  </si>
+  <si>
+    <t>MR2609/0565</t>
+  </si>
+  <si>
+    <t>220KV_220KV Itarsi PGCIL No.-2 Feeder</t>
+  </si>
+  <si>
+    <t>220KV_ITARSI</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Testing and Bay Maintanence work.</t>
+  </si>
+  <si>
+    <t>J.D.Khoria</t>
+  </si>
+  <si>
+    <t>9425804975</t>
+  </si>
+  <si>
+    <t>MR2609/0566</t>
+  </si>
+  <si>
+    <t>132KV_132/33 KV 40 MVA IMP-1</t>
+  </si>
+  <si>
+    <t>132KV_KARAPGAON</t>
+  </si>
+  <si>
+    <t>SD FOR POST MOONSOON MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>RANJEET KORI</t>
+  </si>
+  <si>
+    <t>9425806701</t>
   </si>
   <si>
     <t>MR2609/0510</t>
@@ -361,40 +415,25 @@
     <t>8717944384</t>
   </si>
   <si>
-    <t>MR2609/0526</t>
-  </si>
-  <si>
-    <t>132KV_50mva TAL X-MER</t>
-  </si>
-  <si>
-    <t>132KV_KHIRKIYA</t>
-  </si>
-  <si>
-    <t>POST MONSOON MAINTANANCE &amp; TESTING WORK</t>
-  </si>
-  <si>
-    <t>R.K VAMNE</t>
-  </si>
-  <si>
-    <t>9425805830</t>
-  </si>
-  <si>
-    <t>MR2609/0527</t>
-  </si>
-  <si>
-    <t>40MVA_132/33KV_BHEL_X'mer</t>
-  </si>
-  <si>
-    <t>post monsoon maintanance &amp; testing work</t>
-  </si>
-  <si>
-    <t>29-09-2026 13:30:00</t>
-  </si>
-  <si>
-    <t>29-09-2026 17:30:00</t>
-  </si>
-  <si>
-    <t>MR2609/0542</t>
+    <t>MR2609/0580</t>
+  </si>
+  <si>
+    <t>132KV_132 kv katni kymore ckt 2 line</t>
+  </si>
+  <si>
+    <t>400KV_KATNI4</t>
+  </si>
+  <si>
+    <t>F/O disc replacement &amp; Other line maintenance wor</t>
+  </si>
+  <si>
+    <t>manoj kumar tiwari</t>
+  </si>
+  <si>
+    <t>9425804993</t>
+  </si>
+  <si>
+    <t>MR2609/0583</t>
   </si>
   <si>
     <t>132KV_132 kv Kotar  â¿¿  Rampur Baghelan line</t>
@@ -412,24 +451,6 @@
     <t>9407070182</t>
   </si>
   <si>
-    <t>MR2609/0558</t>
-  </si>
-  <si>
-    <t>132KV_132kv Main Bus, 50MVA BHEL X-MER, 132kV Maihar 1&amp;2 feeder, 132kv Kymore Barhi 2 feeder</t>
-  </si>
-  <si>
-    <t>132KV_KYMORE</t>
-  </si>
-  <si>
-    <t>For replacement of 132kv Bus dividing isolator</t>
-  </si>
-  <si>
-    <t>SK chaturvedi</t>
-  </si>
-  <si>
-    <t>9425806938</t>
-  </si>
-  <si>
     <t>MR2609/0450</t>
   </si>
   <si>
@@ -454,139 +475,133 @@
     <t>9425805120</t>
   </si>
   <si>
-    <t>MR2609/0524</t>
-  </si>
-  <si>
-    <t>220KV_160MVA Transformers-1 (BHEL)</t>
+    <t>MR2609/0591</t>
+  </si>
+  <si>
+    <t>132KV_20MVA GEC XMER</t>
+  </si>
+  <si>
+    <t>132KV_MANDLA</t>
+  </si>
+  <si>
+    <t>For VCB and 33KV C&amp;R Panel replacement</t>
+  </si>
+  <si>
+    <t>CHETAN YADAV</t>
+  </si>
+  <si>
+    <t>9424316543</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA -I (BHEL)</t>
   </si>
   <si>
     <t>400KV_MANDSOUR4</t>
   </si>
   <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>carrying out Post Monsoon Maintenance work.</t>
-  </si>
-  <si>
-    <t>CP DHAKAD</t>
-  </si>
-  <si>
-    <t>9907804919</t>
-  </si>
-  <si>
-    <t>MR2609/0540</t>
-  </si>
-  <si>
-    <t>132KV_132/33 KV 63 MVA BBL X-MER -1</t>
+    <t>Post Monsoon Maintenance work</t>
+  </si>
+  <si>
+    <t>K.C. PANWAR</t>
+  </si>
+  <si>
+    <t>7587951066</t>
+  </si>
+  <si>
+    <t>MR2609/0564</t>
+  </si>
+  <si>
+    <t>MR2609/0584</t>
+  </si>
+  <si>
+    <t>132KV_132KV MORWA-BINA U.P(INTER STATE) CKT</t>
+  </si>
+  <si>
+    <t>132KV_MORWA</t>
+  </si>
+  <si>
+    <t>FLASH OVER DISC REPLACEMENT WORK</t>
+  </si>
+  <si>
+    <t>G.L SAHU</t>
+  </si>
+  <si>
+    <t>9425805102</t>
+  </si>
+  <si>
+    <t>MR2609/0604</t>
+  </si>
+  <si>
+    <t>220KV_220 kv Narsinghpur-sukha-II feeder</t>
   </si>
   <si>
     <t>220KV_NARSINGHPUR</t>
   </si>
   <si>
-    <t>POST MOONSOON MAINTENANCE WORK</t>
-  </si>
-  <si>
-    <t>DINESH KUSHWAHA</t>
+    <t>for replacement loop jumpher ct top clamp b phase</t>
+  </si>
+  <si>
+    <t>30-09-2026 14:00:00</t>
+  </si>
+  <si>
+    <t>Dinesh kushwaha</t>
   </si>
   <si>
     <t>9425182413</t>
   </si>
   <si>
-    <t>MR2609/0525</t>
-  </si>
-  <si>
-    <t>220KV_220KV Bus- Coupler</t>
+    <t>MR2609/0605</t>
+  </si>
+  <si>
+    <t>220KV_220 kv Narsinghpur -Jabalpur-1 feeder</t>
+  </si>
+  <si>
+    <t>Y phase CB top clamp toop jumper replacement work</t>
+  </si>
+  <si>
+    <t>30-09-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>Dinesh Kushwaha</t>
+  </si>
+  <si>
+    <t>MR2609/0590</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch Mandsaur Circuit IInd</t>
   </si>
   <si>
     <t>220KV_NEEMUCH</t>
   </si>
   <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
-    <t>For safety purpose</t>
-  </si>
-  <si>
-    <t>S.H. Mansuri</t>
-  </si>
-  <si>
-    <t>7587951068</t>
-  </si>
-  <si>
-    <t>MR2609/0516</t>
-  </si>
-  <si>
-    <t>220KV_220/132KV 160MVA CGL X-Mer</t>
-  </si>
-  <si>
-    <t>Post - monsoon maintenance &amp; CT replacement work</t>
-  </si>
-  <si>
-    <t>MR2609/0532</t>
-  </si>
-  <si>
-    <t>132KV_40MVA Transformer Ist BHEL</t>
-  </si>
-  <si>
-    <t>220KV_PANDHURNA</t>
-  </si>
-  <si>
-    <t>Post Monsoon Maintenance</t>
-  </si>
-  <si>
-    <t>Sanjay Shende</t>
-  </si>
-  <si>
-    <t>9425811447</t>
-  </si>
-  <si>
-    <t>132KV_PATERA</t>
-  </si>
-  <si>
-    <t>CB Y phase pole hot point attanding work</t>
-  </si>
-  <si>
-    <t>MR2609/0544</t>
-  </si>
-  <si>
-    <t>132KV_132KV Semariya Line</t>
-  </si>
-  <si>
-    <t>MR2609/0545</t>
-  </si>
-  <si>
-    <t>132KV_40MVA BBL XMER 01</t>
-  </si>
-  <si>
-    <t>220KV_PICHHORE</t>
-  </si>
-  <si>
-    <t>Post monsoon maintenance work</t>
-  </si>
-  <si>
-    <t>Virendra K ahirwar</t>
-  </si>
-  <si>
-    <t>9425801438</t>
-  </si>
-  <si>
-    <t>MR2609/0546</t>
-  </si>
-  <si>
-    <t>132KV_50MVA XMER -II BHEL</t>
-  </si>
-  <si>
-    <t>MR2609/0560</t>
-  </si>
-  <si>
-    <t>400KV_400kV Pithampur-Indore PGCIL Ckt -2</t>
+    <t>For Line Maintenance work</t>
+  </si>
+  <si>
+    <t>30-09-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>MR2609/0589</t>
+  </si>
+  <si>
+    <t>220KV_220KV Neemuch Mandsaur Circuit Ist</t>
+  </si>
+  <si>
+    <t>MR2609/0557</t>
+  </si>
+  <si>
+    <t>220KV_220kV Interconnector ckt-1st</t>
   </si>
   <si>
     <t>400KV_PITHAMPUR4</t>
   </si>
   <si>
-    <t>for bay maintenance and testing work</t>
+    <t>For Replacement of R-ph Damaged conductor</t>
+  </si>
+  <si>
+    <t>30-09-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>30-09-2026 17:30:00</t>
   </si>
   <si>
     <t>Rajudas bairagi</t>
@@ -595,34 +610,28 @@
     <t>9425801532</t>
   </si>
   <si>
-    <t>MR2609/0548</t>
-  </si>
-  <si>
-    <t>132KV_132kV Raghogarh GAIL line</t>
-  </si>
-  <si>
-    <t>132KV_RAGHOGARH</t>
-  </si>
-  <si>
-    <t>For Line maintenance work</t>
-  </si>
-  <si>
-    <t>Akhilesh Singh</t>
-  </si>
-  <si>
-    <t>8586865656</t>
-  </si>
-  <si>
-    <t>MR2609/0530</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA Xâ¿¿mer-2nd   (BHEL)</t>
+    <t>MR2609/0556</t>
+  </si>
+  <si>
+    <t>220KV_220kV Interconnector ckt-2nd</t>
+  </si>
+  <si>
+    <t>For replacement of Y-ph damaged conductor</t>
+  </si>
+  <si>
+    <t>30-09-2026 09:30:00</t>
+  </si>
+  <si>
+    <t>MR2609/0586</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA Xâ¿¿mer-Ist (AREVA)</t>
   </si>
   <si>
     <t>220KV_RAJGARH (BIAORA)</t>
   </si>
   <si>
-    <t>Post mansoon maintenance and Testing work</t>
+    <t>Bay Maintenance work</t>
   </si>
   <si>
     <t>NEELESH BASTRI</t>
@@ -631,16 +640,16 @@
     <t>9425804342</t>
   </si>
   <si>
-    <t>MR2609/0547</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA X-mer-II (Make-ALSTOM )</t>
-  </si>
-  <si>
-    <t>132KV_RAJGARH DHAR1</t>
-  </si>
-  <si>
-    <t>For Post Monsoon Maintenance work.</t>
+    <t>MR2609/0598</t>
+  </si>
+  <si>
+    <t>132KV_63MVA X-mer-II (Make-BBL)</t>
+  </si>
+  <si>
+    <t>220KV_RAJGARH DHAR</t>
+  </si>
+  <si>
+    <t>Post monsoon maintenance &amp; Testing work.</t>
   </si>
   <si>
     <t>Er. Kamesh Ninama</t>
@@ -649,7 +658,7 @@
     <t>9713485920</t>
   </si>
   <si>
-    <t>MR2609/0528</t>
+    <t>MR2609/0579</t>
   </si>
   <si>
     <t>220KV_220/132kv, 160 MVA X-MER-I (BHEL)</t>
@@ -658,7 +667,7 @@
     <t>220KV_RATLAM</t>
   </si>
   <si>
-    <t>Post monsoon maintenance &amp; testing work.</t>
+    <t>Post monsoon maintenance &amp; testing work</t>
   </si>
   <si>
     <t>NIKHIL DUNGE</t>
@@ -667,103 +676,73 @@
     <t>9425801487</t>
   </si>
   <si>
-    <t>MR2609/0515</t>
-  </si>
-  <si>
-    <t>220KV_160 mva - I</t>
-  </si>
-  <si>
-    <t>220KV_SAILANA2</t>
-  </si>
-  <si>
-    <t>post mansoon maintananace</t>
-  </si>
-  <si>
-    <t>Rakesh badgotya</t>
-  </si>
-  <si>
-    <t>8305447015</t>
-  </si>
-  <si>
-    <t>MR2609/0518</t>
-  </si>
-  <si>
-    <t>132KV_Sarni - Betul</t>
-  </si>
-  <si>
-    <t>220KV_SARNI</t>
-  </si>
-  <si>
-    <t>Line Maintenance work</t>
-  </si>
-  <si>
-    <t>Ravindra Kumar Marskole</t>
-  </si>
-  <si>
-    <t>9425814080</t>
-  </si>
-  <si>
-    <t>MR2609/0559</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA X-MER - 1st (BHEL)</t>
-  </si>
-  <si>
-    <t>Post -Monsoon Maintenance &amp; Testing work</t>
-  </si>
-  <si>
-    <t>Er. Anup Kumar Dange</t>
-  </si>
-  <si>
-    <t>9425814073</t>
-  </si>
-  <si>
-    <t>MR2609/0550</t>
-  </si>
-  <si>
-    <t>220KV_220 kv Kotar â¿¿ Tons ckt â¿¿ II</t>
-  </si>
-  <si>
-    <t>220KV_SATNA</t>
-  </si>
-  <si>
-    <t>for line maintenance work of 220 kv Kotar â¿¿ Tons c</t>
-  </si>
-  <si>
-    <t>R.K.Prajapati</t>
-  </si>
-  <si>
-    <t>220KV_160MVA CGL X mer No- 3rd</t>
-  </si>
-  <si>
-    <t>220KV_SHUJALPUR</t>
-  </si>
-  <si>
-    <t>Post Monsoon maintenance and Testing work</t>
-  </si>
-  <si>
-    <t>Er.Nitin Narayan Verma</t>
-  </si>
-  <si>
-    <t>9981559007</t>
-  </si>
-  <si>
-    <t>MR2609/0523</t>
-  </si>
-  <si>
-    <t>MR2609/0536</t>
-  </si>
-  <si>
-    <t>400KV_400KV Singaji Pithampura-1 feeder</t>
+    <t>MR2609/0599</t>
+  </si>
+  <si>
+    <t>132KV_132KV SABALGARH BEERPUR TBCB</t>
+  </si>
+  <si>
+    <t>220KV_SABALGARH</t>
+  </si>
+  <si>
+    <t>LINE MENTENANCE</t>
+  </si>
+  <si>
+    <t>ER. SURAJ PAWAR</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>MR2609/0600</t>
+  </si>
+  <si>
+    <t>220KV_160MVA X-mer 1 CGL</t>
+  </si>
+  <si>
+    <t>220KV_SEONI</t>
+  </si>
+  <si>
+    <t>for oil leakage attending work of CT</t>
+  </si>
+  <si>
+    <t>Arshad Qureshi</t>
+  </si>
+  <si>
+    <t>9425618267</t>
+  </si>
+  <si>
+    <t>132KV_63 MVA X-MER BBL</t>
+  </si>
+  <si>
+    <t>132KV_SEONI MALWA</t>
+  </si>
+  <si>
+    <t>63 MVA X-MER POST MANSOON MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>V P DEWIEDI</t>
+  </si>
+  <si>
+    <t>9425804799</t>
+  </si>
+  <si>
+    <t>MR2609/0573</t>
+  </si>
+  <si>
+    <t>MR2609/0585</t>
+  </si>
+  <si>
+    <t>400KV_400KV Singaji Pithampura-2 feeder</t>
   </si>
   <si>
     <t>400KV_SINGHAJI TPS</t>
   </si>
   <si>
-    <t>400KV Pithampura-1 feeder for relay testing work</t>
-  </si>
-  <si>
-    <t>29-09-2026 19:00:00</t>
+    <t>400KV Pithampura-2 feeder Relay Testing work</t>
+  </si>
+  <si>
+    <t>30-09-2026 19:00:00</t>
   </si>
   <si>
     <t>Deepak Sharma</t>
@@ -772,30 +751,45 @@
     <t>8005696855</t>
   </si>
   <si>
-    <t>MR2609/0529</t>
+    <t>MR2609/0576</t>
+  </si>
+  <si>
+    <t>220KV_220 kv sirmour-Rewa feeder</t>
+  </si>
+  <si>
+    <t>220KV_SIRMOUR</t>
+  </si>
+  <si>
+    <t>R&amp;B phase line to wavetrap bottom clamp &amp; conducto</t>
+  </si>
+  <si>
+    <t>Surendra singh Baheliya</t>
+  </si>
+  <si>
+    <t>7000749021</t>
+  </si>
+  <si>
+    <t>MR2609/0574</t>
+  </si>
+  <si>
+    <t>220KV_Main Circuit breaker 220kv chichli 2 line</t>
+  </si>
+  <si>
+    <t>220KV_UDAIPURA</t>
+  </si>
+  <si>
+    <t>R ph Circuit breaker Hot point attend work</t>
+  </si>
+  <si>
+    <t>Pankaj hariyale</t>
+  </si>
+  <si>
+    <t>9827202680</t>
   </si>
   <si>
     <t>Continuous</t>
   </si>
   <si>
-    <t>400KV_315 MVA Transformer Ist plan shutdown</t>
-  </si>
-  <si>
-    <t>400KV_UJJAIN4</t>
-  </si>
-  <si>
-    <t>post mansoon maintenance work</t>
-  </si>
-  <si>
-    <t>28-09-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>Santosh Chavrasia</t>
-  </si>
-  <si>
-    <t>9425804677</t>
-  </si>
-  <si>
     <t>132KV_WAIDHAN</t>
   </si>
   <si>
@@ -805,9 +799,6 @@
     <t>16-09-2026 08:00:00</t>
   </si>
   <si>
-    <t>30-09-2026 18:00:00</t>
-  </si>
-  <si>
     <t>9425805311</t>
   </si>
   <si>
@@ -820,37 +811,79 @@
     <t>DHARMENDRA  DWIVEDI</t>
   </si>
   <si>
+    <t>sub ld</t>
+  </si>
+  <si>
     <t>ok</t>
   </si>
   <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>deferred, not in WR list</t>
-  </si>
-  <si>
-    <t>sub ld</t>
+    <t>ok, line to be in service</t>
+  </si>
+  <si>
+    <t>ok, EI approval required while shifting line on main tower</t>
+  </si>
+  <si>
+    <t>ok, line to be in service through TBC</t>
+  </si>
+  <si>
+    <t>ok, 132kv Rewa-Rampur baghelan to be in service if required</t>
   </si>
   <si>
     <t>deferred by site</t>
   </si>
   <si>
-    <t xml:space="preserve">deferred, due to s/d on </t>
-  </si>
-  <si>
-    <t>ok, line to be in service</t>
-  </si>
-  <si>
-    <t>deferred due to mandsaur 160MVA x-mer</t>
-  </si>
-  <si>
-    <t>deferred for tomorrow, due to proposed elections</t>
+    <t>deferred , not in WR list</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on seoni 160 MVA and 132kv seoni lakhnadaun line work</t>
   </si>
   <si>
     <t>o&amp;m consent required</t>
   </si>
   <si>
-    <t>APPROVED OUTAGE LIST FOR DATED 29.09.2026</t>
+    <t>apprly for emergency s/d to WRLDC</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>deferred due to s/d on 220kv Main bus at Rajgarh PG</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 30.09.2026</t>
+  </si>
+  <si>
+    <t>400KV/220KV INDORE-ICT-3</t>
+  </si>
+  <si>
+    <t>30-Sep-2026</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>AMP , Dia to be kept open at both sides.</t>
+  </si>
+  <si>
+    <t>RAJGARH - 220KV - BUS 2</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Bus AMP Works and attending hotspot on 206-89B Isolator . Simultaneous outage of 206 Bay is required </t>
+  </si>
+  <si>
+    <t>WR</t>
+  </si>
+  <si>
+    <t>S/I SLDC JABALPUR</t>
   </si>
 </sst>
 </file>
@@ -861,7 +894,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -896,13 +929,27 @@
     </font>
     <font>
       <b/>
-      <sz val="36"/>
+      <sz val="26"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -916,12 +963,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -981,11 +1034,61 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1039,6 +1142,43 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1403,19 +1543,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="5" max="5" width="51" style="12" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="45.85546875" customWidth="1"/>
-    <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" customWidth="1"/>
+    <col min="5" max="5" width="61.5703125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="12" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="47" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="16.5703125" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="32.5703125" style="12" customWidth="1"/>
+    <col min="13" max="13" width="55.5703125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
@@ -1440,20 +1581,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
       <c r="H2" s="18"/>
       <c r="I2" s="18"/>
       <c r="J2" s="18"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="1"/>
       <c r="M2" s="9"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1470,7 +1611,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="1"/>
+      <c r="F3" s="9"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -1495,7 +1636,7 @@
       <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="3" t="s">
@@ -1523,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46293.492349537039</v>
+        <v>46294.667210648149</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
@@ -1532,7 +1673,7 @@
       <c r="E5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="11" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -1554,7 +1695,7 @@
         <v>25</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1563,38 +1704,40 @@
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46293.495219907411</v>
+        <v>46294.486990740741</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E6" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1603,38 +1746,38 @@
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46293.582812499997</v>
+        <v>46294.646597222221</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="K7" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1643,38 +1786,38 @@
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46286.708379629628</v>
+        <v>46294.647789351853</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="4" t="s">
+      <c r="L8" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="M8" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1683,7 +1826,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46293.697650462964</v>
+        <v>46293.644479166665</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>45</v>
@@ -1692,7 +1835,7 @@
       <c r="E9" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="11" t="s">
         <v>47</v>
       </c>
       <c r="G9" s="4" t="s">
@@ -1702,10 +1845,10 @@
         <v>48</v>
       </c>
       <c r="I9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>50</v>
@@ -1714,7 +1857,7 @@
         <v>51</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1723,7 +1866,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46293.58997685185</v>
+        <v>46294.638402777775</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>52</v>
@@ -1732,11 +1875,11 @@
       <c r="E10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>55</v>
@@ -1745,16 +1888,16 @@
         <v>56</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K10" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="L10" s="8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1763,29 +1906,31 @@
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46293.577349537038</v>
+        <v>46293.634722222225</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="11" t="s">
+      <c r="G11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="I11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="J11" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>64</v>
@@ -1794,7 +1939,7 @@
         <v>65</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1803,38 +1948,40 @@
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46293.600590277776</v>
+        <v>46293.637557870374</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E12" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>68</v>
+      <c r="F12" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1843,40 +1990,40 @@
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46293.634722222225</v>
+        <v>46293.636192129627</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1885,40 +2032,38 @@
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46293.637557870374</v>
+        <v>46294.66715277778</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>74</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1927,40 +2072,38 @@
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46293.636192129627</v>
+        <v>46294.566666666666</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="4" t="s">
         <v>74</v>
       </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>68</v>
+        <v>75</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>76</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1969,38 +2112,38 @@
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46293.630520833336</v>
+        <v>46294.579039351855</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="J16" s="6" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2009,38 +2152,38 @@
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46293.640266203707</v>
+        <v>46288.66915509259</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>93</v>
-      </c>
       <c r="M17" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2049,38 +2192,38 @@
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46293.595682870371</v>
+        <v>46294.597951388889</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>96</v>
+        <v>91</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="M18" s="11" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2089,38 +2232,38 @@
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46293.597187500003</v>
+        <v>46294.516608796293</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="I19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>99</v>
-      </c>
       <c r="L19" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M19" s="11" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2129,40 +2272,38 @@
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46292.626782407409</v>
+        <v>46294.635393518518</v>
       </c>
       <c r="C20" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>111</v>
-      </c>
       <c r="M20" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2171,38 +2312,38 @@
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>46293.518900462965</v>
+        <v>46294.510266203702</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>114</v>
+        <v>106</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>107</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="M21" s="11" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2211,38 +2352,38 @@
         <v>18</v>
       </c>
       <c r="B22" s="5">
-        <v>46293.522499999999</v>
+        <v>46294.419502314813</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="L22" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M22" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2251,38 +2392,38 @@
         <v>19</v>
       </c>
       <c r="B23" s="5">
-        <v>46293.602743055555</v>
+        <v>46294.436805555553</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>118</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2291,38 +2432,40 @@
         <v>20</v>
       </c>
       <c r="B24" s="5">
-        <v>46293.65121527778</v>
+        <v>46292.626782407409</v>
       </c>
       <c r="C24" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>134</v>
-      </c>
       <c r="M24" s="11" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2331,40 +2474,38 @@
         <v>21</v>
       </c>
       <c r="B25" s="5">
-        <v>46289.514745370368</v>
+        <v>46294.547858796293</v>
       </c>
       <c r="C25" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>142</v>
-      </c>
       <c r="M25" s="11" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2373,38 +2514,38 @@
         <v>22</v>
       </c>
       <c r="B26" s="5">
-        <v>46293.509652777779</v>
+        <v>46294.569699074076</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>145</v>
+        <v>137</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>138</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="M26" s="11" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2413,38 +2554,40 @@
         <v>23</v>
       </c>
       <c r="B27" s="5">
-        <v>46293.598136574074</v>
+        <v>46289.514745370368</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D27" s="4"/>
+        <v>142</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>27</v>
+      </c>
       <c r="E27" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>152</v>
+        <v>143</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>144</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="M27" s="11" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2453,38 +2596,38 @@
         <v>24</v>
       </c>
       <c r="B28" s="5">
-        <v>46293.518611111111</v>
+        <v>46294.588969907411</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>152</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>159</v>
+        <v>20</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="M28" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2493,38 +2636,38 @@
         <v>25</v>
       </c>
       <c r="B29" s="5">
-        <v>46293.456574074073</v>
+        <v>46294.400277777779</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F29" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H29" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="I29" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="H29" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>161</v>
-      </c>
       <c r="L29" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2533,38 +2676,38 @@
         <v>26</v>
       </c>
       <c r="B30" s="5">
-        <v>46293.572905092595</v>
+        <v>46294.573391203703</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="L30" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>171</v>
-      </c>
       <c r="M30" s="11" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2573,38 +2716,38 @@
         <v>27</v>
       </c>
       <c r="B31" s="5">
-        <v>46293.619016203702</v>
+        <v>46294.702835648146</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="11" t="s">
-        <v>175</v>
-      </c>
-      <c r="F31" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="4" t="s">
+      <c r="K31" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="L31" s="8" t="s">
-        <v>59</v>
+        <v>174</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2613,38 +2756,38 @@
         <v>28</v>
       </c>
       <c r="B32" s="5">
-        <v>46293.623263888891</v>
+        <v>46294.70758101852</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="I32" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="4" t="s">
+      <c r="J32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="I32" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>180</v>
-      </c>
       <c r="L32" s="8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2653,38 +2796,38 @@
         <v>29</v>
       </c>
       <c r="B33" s="5">
-        <v>46293.625335648147</v>
+        <v>46294.585775462961</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="I33" s="6" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2693,38 +2836,38 @@
         <v>30</v>
       </c>
       <c r="B34" s="5">
-        <v>46293.660995370374</v>
+        <v>46294.584224537037</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="F34" s="4" t="s">
         <v>186</v>
       </c>
+      <c r="F34" s="11" t="s">
+        <v>182</v>
+      </c>
       <c r="G34" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>189</v>
+        <v>149</v>
       </c>
       <c r="M34" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2733,38 +2876,38 @@
         <v>31</v>
       </c>
       <c r="B35" s="5">
-        <v>46293.627627314818</v>
+        <v>46293.649918981479</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="J35" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" s="4" t="s">
+      <c r="K35" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="I35" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K35" s="7" t="s">
+      <c r="L35" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="L35" s="8" t="s">
-        <v>195</v>
-      </c>
       <c r="M35" s="11" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2773,38 +2916,38 @@
         <v>32</v>
       </c>
       <c r="B36" s="5">
-        <v>46293.549826388888</v>
+        <v>46293.647916666669</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="I36" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="J36" s="6" t="s">
-        <v>57</v>
+        <v>191</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2813,38 +2956,38 @@
         <v>33</v>
       </c>
       <c r="B37" s="5">
-        <v>46293.626168981478</v>
+        <v>46294.578356481485</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>201</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>22</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="K37" s="7" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="M37" s="11" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2853,38 +2996,38 @@
         <v>34</v>
       </c>
       <c r="B38" s="5">
-        <v>46293.538356481484</v>
+        <v>46294.654456018521</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="L38" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="L38" s="8" t="s">
-        <v>213</v>
-      </c>
       <c r="M38" s="11" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2893,38 +3036,38 @@
         <v>35</v>
       </c>
       <c r="B39" s="5">
-        <v>46293.387800925928</v>
+        <v>46294.528587962966</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K39" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="L39" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="L39" s="8" t="s">
-        <v>219</v>
-      </c>
       <c r="M39" s="11" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2933,38 +3076,38 @@
         <v>36</v>
       </c>
       <c r="B40" s="5">
-        <v>46293.495162037034</v>
+        <v>46294.661157407405</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K40" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="L40" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="L40" s="8" t="s">
-        <v>225</v>
-      </c>
       <c r="M40" s="11" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2973,38 +3116,38 @@
         <v>37</v>
       </c>
       <c r="B41" s="5">
-        <v>46293.65929398148</v>
+        <v>46294.666238425925</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="K41" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="4" t="s">
+      <c r="L41" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="I41" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="L41" s="8" t="s">
-        <v>230</v>
-      </c>
       <c r="M41" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3013,38 +3156,38 @@
         <v>38</v>
       </c>
       <c r="B42" s="5">
-        <v>46293.633877314816</v>
+        <v>46294.487303240741</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K42" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="L42" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="G42" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="L42" s="8" t="s">
-        <v>128</v>
-      </c>
       <c r="M42" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3053,16 +3196,16 @@
         <v>39</v>
       </c>
       <c r="B43" s="5">
-        <v>46293.506724537037</v>
+        <v>46294.578113425923</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="11" t="s">
         <v>237</v>
       </c>
       <c r="G43" s="4" t="s">
@@ -3072,19 +3215,19 @@
         <v>238</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>30</v>
+        <v>239</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L43" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M43" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3093,7 +3236,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="5">
-        <v>46293.594409722224</v>
+        <v>46294.514837962961</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>242</v>
@@ -3102,7 +3245,7 @@
       <c r="E44" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="11" t="s">
         <v>244</v>
       </c>
       <c r="G44" s="4" t="s">
@@ -3112,19 +3255,19 @@
         <v>245</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="K44" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="K44" s="7" t="s">
+      <c r="L44" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="L44" s="8" t="s">
-        <v>248</v>
-      </c>
       <c r="M44" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3133,89 +3276,185 @@
         <v>41</v>
       </c>
       <c r="B45" s="5">
-        <v>46293.548159722224</v>
+        <v>46294.498136574075</v>
       </c>
       <c r="C45" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="F45" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="E45" s="11" t="s">
+      <c r="G45" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="F45" s="4" t="s">
+      <c r="I45" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="K45" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="H45" s="4" t="s">
+      <c r="L45" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="M45" s="11" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="20">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B46" s="21">
+        <v>46259.788923611108</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D46" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="J45" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K45" s="7" t="s">
+      <c r="E46" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="F46" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="L45" s="8" t="s">
+      <c r="G46" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="M45" s="4" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B46" s="5">
-        <v>46259.788923611108</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="F46" s="4" t="s">
+      <c r="I46" s="23" t="s">
         <v>257</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="4" t="s">
+      <c r="J46" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="L46" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="I46" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="K46" s="7" t="s">
+      <c r="M46" s="22" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="32">
+        <v>43</v>
+      </c>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="F47" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="G47" s="26"/>
+      <c r="H47" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="I47" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="J47" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="K47" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="L47" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="M47" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="L46" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="M46" s="11" t="s">
-        <v>269</v>
-      </c>
+    </row>
+    <row r="48" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="32">
+        <v>44</v>
+      </c>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="F48" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="G48" s="26"/>
+      <c r="H48" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="I48" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="J48" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="K48" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="L48" s="27" t="s">
+        <v>280</v>
+      </c>
+      <c r="M48" s="29" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="26"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="31" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="26"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="26"/>
+      <c r="K50" s="26"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$17</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$34</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="235">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -76,25 +76,457 @@
     <t>REMARK</t>
   </si>
   <si>
-    <t>MR2610/0484</t>
-  </si>
-  <si>
-    <t>220KV_220 kV GOrabazar- Amarkantak</t>
-  </si>
-  <si>
-    <t>220KV_GORABAZAR</t>
+    <t>MR2610/0494</t>
+  </si>
+  <si>
+    <t>132KV_63 MVA X-MER BBL</t>
+  </si>
+  <si>
+    <t>220KV_ASHOKNAGAR</t>
   </si>
   <si>
     <t>NON-OCCM-MP</t>
   </si>
   <si>
+    <t>POST MANSOON MAINT.</t>
+  </si>
+  <si>
+    <t>21-10-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>21-10-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>RAKESH SUMAN</t>
+  </si>
+  <si>
+    <t>7587951093</t>
+  </si>
+  <si>
+    <t>MR2610/0499</t>
+  </si>
+  <si>
+    <t>400KV_315 MVA X-MER NO.2 MAKE CGL</t>
+  </si>
+  <si>
+    <t>400KV_ASHTA4</t>
+  </si>
+  <si>
+    <t>POST MANSOON MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>21-10-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>DEVESH KUMAR UIKEY</t>
+  </si>
+  <si>
+    <t>7987106006</t>
+  </si>
+  <si>
+    <t>MR2610/0503</t>
+  </si>
+  <si>
+    <t>220KV_220KV Ashta - Dewas line</t>
+  </si>
+  <si>
+    <t>For overhead stringing of new 220KV line</t>
+  </si>
+  <si>
+    <t>Sandeep Umredkar</t>
+  </si>
+  <si>
+    <t>9425820035</t>
+  </si>
+  <si>
+    <t>MR2610/0506</t>
+  </si>
+  <si>
+    <t>220KV_220KV Ashta - Chapda line</t>
+  </si>
+  <si>
+    <t>For stringing of new 220KV line</t>
+  </si>
+  <si>
+    <t>MR2610/0496</t>
+  </si>
+  <si>
+    <t>132KV_132KV Birshinghpur-Shahdol ckt-I</t>
+  </si>
+  <si>
+    <t>220KV_BIRSINGHPUR</t>
+  </si>
+  <si>
+    <t>For Jumper cone Tightening &amp; other line work</t>
+  </si>
+  <si>
+    <t>Jagdish Prasad Ashati</t>
+  </si>
+  <si>
+    <t>9424445533</t>
+  </si>
+  <si>
+    <t>MR2610/0505</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA BBL X-MER-I</t>
+  </si>
+  <si>
+    <t>132KV_CHANDERI</t>
+  </si>
+  <si>
+    <t>post-monsoon Maintenance and testing work</t>
+  </si>
+  <si>
+    <t>21-10-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>Lalit Singh</t>
+  </si>
+  <si>
+    <t>9425806845</t>
+  </si>
+  <si>
+    <t>MR2610/0491</t>
+  </si>
+  <si>
+    <t>220KV_220/132/33 KV 160 MVA Transformer-II make BHEL</t>
+  </si>
+  <si>
+    <t>220KV_DALODA</t>
+  </si>
+  <si>
+    <t>for carrying out post monsoon maintenance work.</t>
+  </si>
+  <si>
+    <t>SHAILENDRA BORASI</t>
+  </si>
+  <si>
+    <t>9907246485</t>
+  </si>
+  <si>
+    <t>MR2610/0509</t>
+  </si>
+  <si>
+    <t>220KV_160MVA X-MER 2nd EMCO</t>
+  </si>
+  <si>
+    <t>220KV_DEWAS</t>
+  </si>
+  <si>
+    <t>for Post mansoon maint.</t>
+  </si>
+  <si>
+    <t>21-10-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Sh.A.K. JOSHI</t>
+  </si>
+  <si>
+    <t>9424887657</t>
+  </si>
+  <si>
+    <t>MR2610/0497</t>
+  </si>
+  <si>
+    <t>132KV_132/33KV 50MVA XMER BHEL</t>
+  </si>
+  <si>
+    <t>132KV_GUDGAON</t>
+  </si>
+  <si>
+    <t>Post monsoon maintenance and testing work</t>
+  </si>
+  <si>
+    <t>Sanjay pawar</t>
+  </si>
+  <si>
+    <t>9425802293</t>
+  </si>
+  <si>
+    <t>MR2610/0481</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA BHEL XMER 220/132/33 KV</t>
+  </si>
+  <si>
+    <t>220KV_HOSHANGABAD</t>
+  </si>
+  <si>
+    <t>POST MONSOON MAINTENANCE &amp; TESTING WORK</t>
+  </si>
+  <si>
+    <t>21-10-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>V.P.DWIVEDI</t>
+  </si>
+  <si>
+    <t>9425804799</t>
+  </si>
+  <si>
+    <t>MR2610/0489</t>
+  </si>
+  <si>
+    <t>132KV_132/33 kv 63 mva x mer BBL</t>
+  </si>
+  <si>
+    <t>220KV_JABALPUR</t>
+  </si>
+  <si>
+    <t>post monsoon maintenance and testing work</t>
+  </si>
+  <si>
+    <t>sunil shukla</t>
+  </si>
+  <si>
+    <t>7648817157</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>400KV_JP BINA</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>22-10-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>7987976012</t>
+  </si>
+  <si>
+    <t>MR2609/0609</t>
+  </si>
+  <si>
+    <t>400KV_400KV_400KV BUS-2 (BUS-B)</t>
+  </si>
+  <si>
+    <t>PM of BUS-2 (BUS-B, BAY-1 &amp; BAY-5)</t>
+  </si>
+  <si>
+    <t>20-10-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>31-10-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>KRISHNA SINGH THAKUR</t>
+  </si>
+  <si>
+    <t>MR2610/0469</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>400KV_400kV Kirnapur Bhilai Line</t>
+  </si>
+  <si>
+    <t>400KV_KIRNAPUR</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Conductor Vibration Damper Provide &amp; Suspension Cl</t>
+  </si>
+  <si>
+    <t>19-10-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
+  </si>
+  <si>
+    <t>MR2610/0504</t>
+  </si>
+  <si>
+    <t>40MVA_132/33KV_IMP-I_X'mer</t>
+  </si>
+  <si>
+    <t>132KV_LATERI</t>
+  </si>
+  <si>
+    <t>POST MANSOON MAINTENANCE</t>
+  </si>
+  <si>
+    <t>MAHENDRA SAHU</t>
+  </si>
+  <si>
+    <t>9425804982</t>
+  </si>
+  <si>
+    <t>MR2610/0486</t>
+  </si>
+  <si>
+    <t>220KV_220KV_200MVA X-mer Make CGL</t>
+  </si>
+  <si>
+    <t>220KV_MALANPUR</t>
+  </si>
+  <si>
+    <t>Post Monsoon Maintenance work</t>
+  </si>
+  <si>
+    <t>21-10-2026 10:30:00</t>
+  </si>
+  <si>
+    <t>Vikram Ahirwar</t>
+  </si>
+  <si>
+    <t>9425805415</t>
+  </si>
+  <si>
+    <t>MR2609/0610</t>
+  </si>
+  <si>
+    <t>132KV_132 kv 50 MVA Xmer &amp; 33 kv Half Main Bus Section-l</t>
+  </si>
+  <si>
+    <t>Post Monsoon Maint. &amp; Hot point attend work</t>
+  </si>
+  <si>
+    <t>01-10-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>27-10-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>9039761183</t>
+  </si>
+  <si>
+    <t>MR2610/0507</t>
+  </si>
+  <si>
+    <t>160MVA_220/132KV_CGL_X'mer_1</t>
+  </si>
+  <si>
+    <t>220KV_MEHGAON</t>
+  </si>
+  <si>
+    <t>Post monsoon</t>
+  </si>
+  <si>
+    <t>Asheesh kumar</t>
+  </si>
+  <si>
+    <t>8319926224</t>
+  </si>
+  <si>
+    <t>MR2610/0502</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Moondi - Kalisindh PH-1 &amp; PH-2 (NVDA) Line</t>
+  </si>
+  <si>
+    <t>132KV_MOONDI</t>
+  </si>
+  <si>
+    <t>For Jumper Tightening &amp; Other Line Maint. work</t>
+  </si>
+  <si>
+    <t>Nitin Girdonia</t>
+  </si>
+  <si>
+    <t>9425804899</t>
+  </si>
+  <si>
+    <t>MR2610/0466</t>
+  </si>
+  <si>
+    <t>For Tower Final Checking &amp; Stringing 2 ckt entire</t>
+  </si>
+  <si>
+    <t>17-10-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>MR2610/0492</t>
+  </si>
+  <si>
+    <t>400KV_315 MVA ICT-IV</t>
+  </si>
+  <si>
+    <t>400KV_NAGDA4</t>
+  </si>
+  <si>
+    <t>YASHVANT RAI</t>
+  </si>
+  <si>
+    <t>9981302592</t>
+  </si>
+  <si>
+    <t>MR2610/0304</t>
+  </si>
+  <si>
+    <t>132KV_132kV Nainpur-Ghansour Line</t>
+  </si>
+  <si>
+    <t>132KV_NAINPUR</t>
+  </si>
+  <si>
+    <t>OPGW stringing work</t>
+  </si>
+  <si>
+    <t>14-10-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>25-10-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>Amol Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2610/0498</t>
+  </si>
+  <si>
+    <t>132KV_132/33 KV 40 MVA TELK Xmer</t>
+  </si>
+  <si>
+    <t>132KV_NARSINGHPUR1</t>
+  </si>
+  <si>
+    <t>post monsoon maintenance work</t>
+  </si>
+  <si>
+    <t>Jayprakash Dharne</t>
+  </si>
+  <si>
+    <t>7587951106</t>
+  </si>
+  <si>
+    <t>MR2610/0495</t>
+  </si>
+  <si>
+    <t>132KV_132/33KV 50MVA BBL MAKE XMER</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>IMRAN KHAN</t>
+  </si>
+  <si>
+    <t>9993661506</t>
+  </si>
+  <si>
+    <t>MR2610/0488</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Panagar- Birsinghpur</t>
+  </si>
+  <si>
     <t>Jumper tightening by Contract basis</t>
   </si>
   <si>
-    <t>20-10-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>20-10-2026 18:00:00</t>
+    <t>28-10-2026 18:00:00</t>
   </si>
   <si>
     <t>Jitendra Tiwari</t>
@@ -103,240 +535,199 @@
     <t>9425805298</t>
   </si>
   <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>400KV_JP BINA</t>
-  </si>
-  <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
-    <t>22-10-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>7987976012</t>
-  </si>
-  <si>
-    <t>MR2609/0609</t>
-  </si>
-  <si>
-    <t>400KV_400KV_400KV BUS-2 (BUS-B)</t>
-  </si>
-  <si>
-    <t>PM of BUS-2 (BUS-B, BAY-1 &amp; BAY-5)</t>
-  </si>
-  <si>
-    <t>20-10-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>31-10-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>KRISHNA SINGH THAKUR</t>
-  </si>
-  <si>
-    <t>MR2610/0469</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>400KV_400kV Kirnapur Bhilai Line</t>
-  </si>
-  <si>
-    <t>400KV_KIRNAPUR</t>
-  </si>
-  <si>
-    <t>OCCM-MP</t>
-  </si>
-  <si>
-    <t>Conductor Vibration Damper Provide &amp; Suspension Cl</t>
-  </si>
-  <si>
-    <t>19-10-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>S.K. BHALADHARE</t>
-  </si>
-  <si>
-    <t>9425807264</t>
-  </si>
-  <si>
-    <t>MR2609/0610</t>
-  </si>
-  <si>
-    <t>132KV_132 kv 50 MVA Xmer &amp; 33 kv Half Main Bus Section-l</t>
-  </si>
-  <si>
-    <t>220KV_MALANPUR</t>
-  </si>
-  <si>
-    <t>Post Monsoon Maint. &amp; Hot point attend work</t>
-  </si>
-  <si>
-    <t>01-10-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>27-10-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Vikram Ahirwar</t>
-  </si>
-  <si>
-    <t>9039761183</t>
-  </si>
-  <si>
-    <t>MR2610/0466</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Moondi - Kalisindh PH-1 &amp; PH-2 (NVDA) Line</t>
-  </si>
-  <si>
-    <t>132KV_MOONDI</t>
-  </si>
-  <si>
-    <t>For Tower Final Checking &amp; Stringing 2 ckt entire</t>
-  </si>
-  <si>
-    <t>17-10-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>Nitin Girdonia</t>
-  </si>
-  <si>
-    <t>9425804899</t>
-  </si>
-  <si>
-    <t>MR2610/0304</t>
-  </si>
-  <si>
-    <t>132KV_132kV Nainpur-Ghansour Line</t>
-  </si>
-  <si>
-    <t>132KV_NAINPUR</t>
-  </si>
-  <si>
-    <t>OPGW stringing work</t>
-  </si>
-  <si>
-    <t>14-10-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>25-10-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>Amol Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>MR2609/0636</t>
-  </si>
-  <si>
-    <t>220KV_220KV Omkareshwar Khandwa PGCIl line</t>
-  </si>
-  <si>
-    <t>220KV_OMKARESHWAR</t>
-  </si>
-  <si>
-    <t>For modification/shifting work</t>
-  </si>
-  <si>
-    <t>03-10-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>Kamal solanki</t>
-  </si>
-  <si>
-    <t>9425805262</t>
-  </si>
-  <si>
-    <t>06-10-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>MR2610/0093</t>
-  </si>
-  <si>
-    <t>220KV_220kv omk-chhegaon line</t>
-  </si>
-  <si>
-    <t>for modification shifting work</t>
-  </si>
-  <si>
-    <t>20-10-2026 20:00:00</t>
-  </si>
-  <si>
-    <t>MR2610/0095</t>
-  </si>
-  <si>
-    <t>220KV_220KV OMK- Julwania line</t>
-  </si>
-  <si>
-    <t>MR2610/0483</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Panagar- Birsinghpur</t>
-  </si>
-  <si>
-    <t>220KV_PANAGAR</t>
-  </si>
-  <si>
-    <t>27-10-2026 18:00:00</t>
+    <t>MR2610/0485</t>
+  </si>
+  <si>
+    <t>132KV_132kv Shivpuri Pichhore Line</t>
+  </si>
+  <si>
+    <t>220KV_PICHHORE</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Suraj Pawar</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>MR2610/0501</t>
+  </si>
+  <si>
+    <t>132KV_132KV 40MVA IMP X-MER</t>
+  </si>
+  <si>
+    <t>132KV_REWA-II (SAGRA)</t>
+  </si>
+  <si>
+    <t>POST MONSOON MAINTENANCE AND TESTING WORK</t>
+  </si>
+  <si>
+    <t>ER. KANISHK SINGH</t>
+  </si>
+  <si>
+    <t>9425804656</t>
+  </si>
+  <si>
+    <t>MR2610/0493</t>
+  </si>
+  <si>
+    <t>132KV_132kv Satna Pawai feeder</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>For attending B-ph CT minor oil leakage and CTwork</t>
+  </si>
+  <si>
+    <t>21-10-2026 15:00:00</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
+  </si>
+  <si>
+    <t>9425813990</t>
+  </si>
+  <si>
+    <t>MR2610/0500</t>
+  </si>
+  <si>
+    <t>132KV_132kV Sidhi - Deosar Ckt - II</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
+  </si>
+  <si>
+    <t>Line maintenance work.</t>
+  </si>
+  <si>
+    <t>G.L Sahu</t>
+  </si>
+  <si>
+    <t>9425805102</t>
+  </si>
+  <si>
+    <t>MR2610/0508</t>
+  </si>
+  <si>
+    <t>132KV_40MVA Transformer-I IMP</t>
+  </si>
+  <si>
+    <t>132KV_SINGHANA</t>
+  </si>
+  <si>
+    <t>Post monsoon maintenance</t>
+  </si>
+  <si>
+    <t>21-10-2026 16:00:00</t>
+  </si>
+  <si>
+    <t>J.C. MUJHALDE</t>
+  </si>
+  <si>
+    <t>9893790114</t>
+  </si>
+  <si>
+    <t>MR2610/0460</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA 2nd bbl-make Transformer</t>
+  </si>
+  <si>
+    <t>220KV_TIKAMGARH</t>
+  </si>
+  <si>
+    <t>Oil leakage attend from bell-Tank</t>
+  </si>
+  <si>
+    <t>31-10-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Pushpendra soni</t>
+  </si>
+  <si>
+    <t>9425806398</t>
+  </si>
+  <si>
+    <t>sub ld</t>
+  </si>
+  <si>
+    <t>ok, through sub ld</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
-    <t>not in WRLDC list</t>
-  </si>
-  <si>
-    <t>under review, please check WRLDC RC1 list</t>
-  </si>
-  <si>
-    <t>sub ld</t>
+    <t>real time as per loading conditions</t>
+  </si>
+  <si>
+    <t>not in WR list</t>
+  </si>
+  <si>
+    <t>deferred due to malanpur 200MVA x-mer s/d</t>
+  </si>
+  <si>
+    <t>ok, through sub ld, ICT 2 to be in service</t>
   </si>
   <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
-    <t>work completed</t>
-  </si>
-  <si>
-    <t>132KV-PENCH-KANHAN-1</t>
-  </si>
-  <si>
-    <t>132KV-MANSAR-MS-PENCH-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To carry out the PID work of Disc Insulator at various location .AR required in Non-Auto mode			
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">To carry out the PID work of Disc Insulator at various location. AR required in Non-Auto mode		
-</t>
-  </si>
-  <si>
-    <t>ok,    A/R in N/A, line to be in service</t>
+    <t>ok, o&amp;m shall be informed</t>
+  </si>
+  <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>400KV-KIRNAPUR-BHILAI-1</t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-MAHALGAON-3</t>
+  </si>
+  <si>
+    <t>220KV-REWA-REWA-MP-2</t>
+  </si>
+  <si>
+    <t>132KV-VSTPS-WAIDHAN-2</t>
+  </si>
+  <si>
+    <t>MP_SLDC</t>
+  </si>
+  <si>
+    <t>FOR PROVIDING VIBRATION DAMPERS AT VARIOUS TOWER LOCATIONS &amp; FOR AUXILIARY ISOLATOR MAINTENANCE WORK</t>
+  </si>
+  <si>
+    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>FOR REPLACEMENT OF EXISTING CONDUCTOR TO HTLS CONDUCTOR WORK</t>
+  </si>
+  <si>
+    <t>09:00</t>
   </si>
   <si>
     <t>10:00</t>
   </si>
   <si>
+    <t>08:00</t>
+  </si>
+  <si>
     <t>18:00</t>
   </si>
   <si>
-    <t>MSLDC_OUTAGE</t>
-  </si>
-  <si>
-    <t>MADHYA PRADESH,MAHARASHTRA</t>
-  </si>
-  <si>
-    <t>S/I, SLDC,MPPTCL, JABALPUR</t>
-  </si>
-  <si>
-    <t>APPROVED OUTAGE LIST FOR DTD. 20.10.26</t>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>real time</t>
+  </si>
+  <si>
+    <t>WR</t>
   </si>
 </sst>
 </file>
@@ -347,7 +738,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -360,25 +751,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -406,7 +793,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -499,19 +886,10 @@
         <color rgb="FF000000"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -519,17 +897,17 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color rgb="FF000000"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -566,35 +944,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -962,23 +1335,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M38"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="55.42578125" customWidth="1"/>
-    <col min="6" max="6" width="24.140625" customWidth="1"/>
+    <col min="5" max="5" width="54.5703125" customWidth="1"/>
+    <col min="6" max="6" width="23.5703125" customWidth="1"/>
     <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="49" customWidth="1"/>
+    <col min="8" max="8" width="50.42578125" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
     <col min="11" max="11" width="26" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="47.28515625" customWidth="1"/>
+    <col min="13" max="13" width="47.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="43.7" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="9" t="s">
         <v>0</v>
@@ -995,28 +1368,26 @@
       <c r="L1" s="10"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="42" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
-      <c r="K2" s="19"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="42" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1039,7 +1410,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="42" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1078,12 +1449,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="33" customHeight="1">
       <c r="A5" s="4">
         <v>1</v>
       </c>
       <c r="B5" s="5">
-        <v>46314.621562499997</v>
+        <v>46315.527939814812</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>17</v>
@@ -1114,464 +1485,1290 @@
         <v>25</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="33" customHeight="1">
       <c r="A6" s="4">
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46294.889849537038</v>
+        <v>46315.590844907405</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="L6" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="M6" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="33" customHeight="1">
       <c r="A7" s="4">
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46312.439849537041</v>
+        <v>46315.643252314818</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>45</v>
-      </c>
       <c r="M7" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="33" customHeight="1">
       <c r="A8" s="4">
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46295.47079861111</v>
+        <v>46315.644918981481</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="33" customHeight="1">
       <c r="A9" s="4">
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46311.720057870371</v>
+        <v>46315.536979166667</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="33" customHeight="1">
       <c r="A10" s="4">
         <v>6</v>
       </c>
       <c r="B10" s="5">
-        <v>46307.565358796295</v>
+        <v>46315.643750000003</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="33" customHeight="1">
       <c r="A11" s="4">
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46295.685486111113</v>
+        <v>46315.511053240742</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="33" customHeight="1">
       <c r="A12" s="4">
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46300.699803240743</v>
+        <v>46315.661828703705</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="33" customHeight="1">
       <c r="A13" s="4">
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46300.707997685182</v>
+        <v>46315.56795138889</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>75</v>
-      </c>
       <c r="M13" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="33" customHeight="1">
       <c r="A14" s="4">
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46314.619768518518</v>
+        <v>46314.474953703706</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="H14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="33" customHeight="1">
+      <c r="A15" s="4">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5">
+        <v>46315.475555555553</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="33" customHeight="1">
+      <c r="A16" s="4">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5">
+        <v>46294.889849537038</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="33" customHeight="1">
+      <c r="A17" s="4">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5">
+        <v>46312.439849537041</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="33" customHeight="1">
+      <c r="A18" s="4">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46315.643518518518</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="33" customHeight="1">
+      <c r="A19" s="4">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5">
+        <v>46315.253958333335</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="33" customHeight="1">
+      <c r="A20" s="4">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46295.47079861111</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="33" customHeight="1">
+      <c r="A21" s="4">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5">
+        <v>46315.650023148148</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="33" customHeight="1">
+      <c r="A22" s="4">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5">
+        <v>46315.63244212963</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="33" customHeight="1">
+      <c r="A23" s="4">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5">
+        <v>46311.720057870371</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="33" customHeight="1">
+      <c r="A24" s="4">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46315.514502314814</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="33" customHeight="1">
+      <c r="A25" s="4">
         <v>21</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="B25" s="5">
+        <v>46307.565358796295</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="33" customHeight="1">
+      <c r="A26" s="4">
         <v>22</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="B26" s="5">
+        <v>46315.576284722221</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="33" customHeight="1">
+      <c r="A27" s="4">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5">
+        <v>46315.533391203702</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="33" customHeight="1">
+      <c r="A28" s="4">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46315.461215277777</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="33" customHeight="1">
+      <c r="A29" s="13">
+        <v>25</v>
+      </c>
+      <c r="B29" s="14">
+        <v>46314.718564814815</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="I29" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="33" customHeight="1">
+      <c r="A30" s="18">
+        <v>26</v>
+      </c>
+      <c r="B30" s="19">
+        <v>46315.624664351853</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="I30" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="L30" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="M30" s="18" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="33" customHeight="1">
+      <c r="A31" s="18">
+        <v>27</v>
+      </c>
+      <c r="B31" s="19">
+        <v>46315.52134259259</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="M31" s="18" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="33" customHeight="1">
+      <c r="A32" s="18">
+        <v>28</v>
+      </c>
+      <c r="B32" s="19">
+        <v>46315.621018518519</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="G32" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="K32" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="M32" s="18" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="33" customHeight="1">
+      <c r="A33" s="18">
+        <v>29</v>
+      </c>
+      <c r="B33" s="19">
+        <v>46315.656435185185</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="G33" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="M33" s="18" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="33" customHeight="1">
+      <c r="A34" s="18">
+        <v>30</v>
+      </c>
+      <c r="B34" s="19">
+        <v>46311.65284722222</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="D34" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
-        <v>11</v>
-      </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="20"/>
-      <c r="H15" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="I15" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="J15" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="L15" s="23"/>
-      <c r="M15" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
-        <v>12</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>101</v>
-      </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>98</v>
-      </c>
-      <c r="J16" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="K16" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="L16" s="23"/>
-      <c r="M16" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L17" s="15"/>
-      <c r="M17" s="16"/>
+      <c r="E34" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="G34" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="M34" s="18" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="45">
+      <c r="A35" s="18">
+        <v>31</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="22">
+        <v>327515</v>
+      </c>
+      <c r="D35" s="21"/>
+      <c r="E35" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="G35" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="I35" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="J35" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="K35" s="21"/>
+      <c r="L35" s="21"/>
+      <c r="M35" s="23" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="45">
+      <c r="A36" s="18">
+        <v>32</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="22">
+        <v>327564</v>
+      </c>
+      <c r="D36" s="21"/>
+      <c r="E36" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="F36" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="G36" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="I36" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="J36" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="K36" s="21"/>
+      <c r="L36" s="21"/>
+      <c r="M36" s="23" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="75">
+      <c r="A37" s="18">
+        <v>33</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="22">
+        <v>327565</v>
+      </c>
+      <c r="D37" s="21"/>
+      <c r="E37" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="G37" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="H37" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="I37" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="J37" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="23" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="30">
+      <c r="A38" s="18">
+        <v>34</v>
+      </c>
+      <c r="B38" s="21"/>
+      <c r="C38" s="22">
+        <v>327609</v>
+      </c>
+      <c r="D38" s="21"/>
+      <c r="E38" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="G38" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="H38" s="22" t="s">
+        <v>227</v>
+      </c>
+      <c r="I38" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="J38" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="K38" s="21"/>
+      <c r="L38" s="21"/>
+      <c r="M38" s="23" t="s">
+        <v>233</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="2">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="E2:K2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="192">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -587,6 +587,18 @@
   </si>
   <si>
     <t>CG SLDC</t>
+  </si>
+  <si>
+    <t>JP-BINA - 400KV - BUS 2</t>
+  </si>
+  <si>
+    <t>JP BINA</t>
+  </si>
+  <si>
+    <t>For overhauling, maintenance &amp; testing of the Pantograph &amp; HCB Isolators (R, Y &amp; B Phases)</t>
+  </si>
+  <si>
+    <t>approved on daily basis by WRLDC</t>
   </si>
 </sst>
 </file>
@@ -656,7 +668,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -779,17 +791,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -846,6 +847,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -886,9 +888,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -1411,7 +1410,7 @@
     </row>
     <row r="7" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A31" si="0">A6+1</f>
+        <f t="shared" ref="A7:A32" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
@@ -2232,38 +2231,38 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="20">
         <v>46319.508055555554</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20" t="s">
+      <c r="D27" s="21"/>
+      <c r="E27" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="20" t="s">
+      <c r="H27" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="I27" s="21" t="s">
+      <c r="I27" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="21" t="s">
+      <c r="J27" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="K27" s="22" t="s">
+      <c r="K27" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="L27" s="23" t="s">
+      <c r="L27" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="M27" s="24" t="s">
+      <c r="M27" s="25" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2272,9 +2271,9 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
       <c r="E28" s="17" t="s">
         <v>176</v>
       </c>
@@ -2287,10 +2286,10 @@
       <c r="H28" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="I28" s="26" t="s">
+      <c r="I28" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="26">
+      <c r="J28" s="27">
         <v>46321.541666666664</v>
       </c>
       <c r="K28" s="17"/>
@@ -2300,45 +2299,45 @@
       </c>
     </row>
     <row r="29" spans="1:13" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="22">
+      <c r="A29" s="23">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="31" t="s">
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="F29" s="31" t="s">
+      <c r="F29" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="G29" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="H29" s="31" t="s">
+      <c r="H29" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="I29" s="32" t="s">
+      <c r="I29" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="J29" s="32" t="s">
+      <c r="J29" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="33" t="s">
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="34" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27">
+      <c r="A30" s="28">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="27"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="28"/>
       <c r="E30" s="17" t="s">
         <v>183</v>
       </c>
@@ -2351,7 +2350,7 @@
       <c r="H30" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="27">
         <v>46321.333333333336</v>
       </c>
       <c r="J30" s="6" t="s">
@@ -2359,18 +2358,18 @@
       </c>
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
-      <c r="M30" s="28" t="s">
+      <c r="M30" s="29" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="27">
+      <c r="A31" s="28">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
       <c r="E31" s="17" t="s">
         <v>185</v>
       </c>
@@ -2383,7 +2382,7 @@
       <c r="H31" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="I31" s="26">
+      <c r="I31" s="27">
         <v>46321.333333333336</v>
       </c>
       <c r="J31" s="6" t="s">
@@ -2396,7 +2395,33 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="34"/>
+      <c r="A32" s="28">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="I32" s="27">
+        <v>46321.333333333336</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
+      <c r="M32" s="19" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="33" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/1.xlsx
+++ b/1.xlsx
@@ -2,27 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NEXT DAY SHUTDOWN\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11205"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="__bookmark_1">Sheet0!$A$1:$M$27</definedName>
+    <definedName name="__bookmark_1">Sheet0!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="308">
   <si>
     <t>STATE LOAD DESPATCH CENTRE 
 Madhya Pradesh Power Transmission Company Limited, Jabalpur</t>
@@ -106,40 +106,349 @@
     <t>9424445533</t>
   </si>
   <si>
-    <t>MR2610/0637</t>
-  </si>
-  <si>
-    <t>132KV_132 kv Chhatarpur naugaon 2 circuit</t>
-  </si>
-  <si>
-    <t>220KV_CHATARPUR</t>
-  </si>
-  <si>
-    <t>For line maintenance and JCT work</t>
-  </si>
-  <si>
-    <t>26-10-2026 10:00:00</t>
-  </si>
-  <si>
-    <t>26-10-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>Pankaj yadav</t>
-  </si>
-  <si>
-    <t>9406813326</t>
-  </si>
-  <si>
-    <t>MR2610/0628</t>
-  </si>
-  <si>
-    <t>220KV_160 MVA AREVA</t>
-  </si>
-  <si>
-    <t>For Post Monsoon maintenance w</t>
-  </si>
-  <si>
-    <t>26-10-2026 09:00:00</t>
+    <t>MR2610/0649</t>
+  </si>
+  <si>
+    <t>132KV_50MVA BHEL Transformer</t>
+  </si>
+  <si>
+    <t>132KV_BEOHARI</t>
+  </si>
+  <si>
+    <t>Post monsoon maintenance and testing work</t>
+  </si>
+  <si>
+    <t>27-10-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>27-10-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>Vijay Kumar Sahu</t>
+  </si>
+  <si>
+    <t>9425814035</t>
+  </si>
+  <si>
+    <t>MR2610/0665</t>
+  </si>
+  <si>
+    <t>132KV_50MVA_Xmer_II_Atlanta</t>
+  </si>
+  <si>
+    <t>132KV_BHANEGAON</t>
+  </si>
+  <si>
+    <t>For Post Monsoon Maintenance work</t>
+  </si>
+  <si>
+    <t>Sandeep Damahe</t>
+  </si>
+  <si>
+    <t>9425805009</t>
+  </si>
+  <si>
+    <t>MR2610/0651</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA BBL-I X-MER-II</t>
+  </si>
+  <si>
+    <t>220KV_BINA</t>
+  </si>
+  <si>
+    <t>post-monsoon Maintenance and testing work</t>
+  </si>
+  <si>
+    <t>27-10-2026 09:30:00</t>
+  </si>
+  <si>
+    <t>Lalit Singh</t>
+  </si>
+  <si>
+    <t>9425806845</t>
+  </si>
+  <si>
+    <t>MR2610/0663</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Bina-Chanderi ckt</t>
+  </si>
+  <si>
+    <t>f/o disc insulator replacement at loc no333B phase</t>
+  </si>
+  <si>
+    <t>27-10-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>Dilip Singh Walkey</t>
+  </si>
+  <si>
+    <t>9425804578</t>
+  </si>
+  <si>
+    <t>MR2610/0664</t>
+  </si>
+  <si>
+    <t>63MVA_132/33KV_BBL_Xmer_1</t>
+  </si>
+  <si>
+    <t>132KV_CHHINDWARA1</t>
+  </si>
+  <si>
+    <t>Post Mansoon Maintenance Work</t>
+  </si>
+  <si>
+    <t>27-10-2026 17:00:00</t>
+  </si>
+  <si>
+    <t>Er. Anju Dhurve</t>
+  </si>
+  <si>
+    <t>9425804752</t>
+  </si>
+  <si>
+    <t>MR2610/0619</t>
+  </si>
+  <si>
+    <t>132KV_132kV Dindori Gorakhpur Line Ckt-I &amp; II Line</t>
+  </si>
+  <si>
+    <t>132KV_DINDORI</t>
+  </si>
+  <si>
+    <t>Hot Line OPGW Work &amp; Other Line Maintenance Work</t>
+  </si>
+  <si>
+    <t>25-10-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>05-11-2026 19:00:00</t>
+  </si>
+  <si>
+    <t>S.K. BHALADHARE</t>
+  </si>
+  <si>
+    <t>9425807264</t>
+  </si>
+  <si>
+    <t>MR2610/0666</t>
+  </si>
+  <si>
+    <t>132KV_132KV ANUPPUR-DONGRITAL CKT</t>
+  </si>
+  <si>
+    <t>132KV_DONGRITAL</t>
+  </si>
+  <si>
+    <t>V.D Provided work</t>
+  </si>
+  <si>
+    <t>G.L SAHU</t>
+  </si>
+  <si>
+    <t>9425805102</t>
+  </si>
+  <si>
+    <t>MR2610/0667</t>
+  </si>
+  <si>
+    <t>132KV_132/33 KV 63 MVA BBL XMER-1</t>
+  </si>
+  <si>
+    <t>132KV_GADARWARA</t>
+  </si>
+  <si>
+    <t>Post mansoon testing &amp; maintenance work</t>
+  </si>
+  <si>
+    <t>MUKESH AGRAWAL</t>
+  </si>
+  <si>
+    <t>9425805687</t>
+  </si>
+  <si>
+    <t>MR2610/0678</t>
+  </si>
+  <si>
+    <t>132KV_132kV Ghansour RTS Feeder</t>
+  </si>
+  <si>
+    <t>132KV_GHANSOUR</t>
+  </si>
+  <si>
+    <t>Old OPGW wire removing work</t>
+  </si>
+  <si>
+    <t>27-10-2026 13:00:00</t>
+  </si>
+  <si>
+    <t>Amol Shende</t>
+  </si>
+  <si>
+    <t>7587951136</t>
+  </si>
+  <si>
+    <t>MR2610/0654</t>
+  </si>
+  <si>
+    <t>220KV_220/132 KV  160 MVA TREANSFORMER</t>
+  </si>
+  <si>
+    <t>220KV_GORABAZAR</t>
+  </si>
+  <si>
+    <t>FOR POST MONSOON MAINTENANCE</t>
+  </si>
+  <si>
+    <t>ASHOK BINGHADE</t>
+  </si>
+  <si>
+    <t>7509148945</t>
+  </si>
+  <si>
+    <t>MR2610/0657</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA X-MER BHEL MAKE</t>
+  </si>
+  <si>
+    <t>220KV_GUDGAON2</t>
+  </si>
+  <si>
+    <t>POST MONSOON MAINTENANCE AND TESTING WORK</t>
+  </si>
+  <si>
+    <t>SANJAY KUMAR PAWAR</t>
+  </si>
+  <si>
+    <t>9425802293</t>
+  </si>
+  <si>
+    <t>MR2610/0650</t>
+  </si>
+  <si>
+    <t>220KV_North zone Indore â¿¿ Indore PGCIL (Hatuniya) CKT - 2 Line.</t>
+  </si>
+  <si>
+    <t>220KV_INDORE-NZ</t>
+  </si>
+  <si>
+    <t>OCCM-MP</t>
+  </si>
+  <si>
+    <t>Line maintenance work and cleaning of disc insulat</t>
+  </si>
+  <si>
+    <t>27-10-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>RAVINDRA PATIL</t>
+  </si>
+  <si>
+    <t>8305612190</t>
+  </si>
+  <si>
+    <t>MR2610/0577</t>
+  </si>
+  <si>
+    <t>Continuous</t>
+  </si>
+  <si>
+    <t>400KV_315MVA ICT-3</t>
+  </si>
+  <si>
+    <t>400KV_INDORE4</t>
+  </si>
+  <si>
+    <t>POSTMANSOON MAINTENANCE</t>
+  </si>
+  <si>
+    <t>28-10-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>ATUL PARADAKR</t>
+  </si>
+  <si>
+    <t>9425804929</t>
+  </si>
+  <si>
+    <t>MR2610/0679</t>
+  </si>
+  <si>
+    <t>132KV_63 MVA ABB TRANSFORMER</t>
+  </si>
+  <si>
+    <t>220KV_JABALPUR</t>
+  </si>
+  <si>
+    <t>TRANSFORMER PAINTING WORK</t>
+  </si>
+  <si>
+    <t>SUNIL SHUKLA</t>
+  </si>
+  <si>
+    <t>7648817157</t>
+  </si>
+  <si>
+    <t>MR2609/0609</t>
+  </si>
+  <si>
+    <t>400KV_400KV_400KV BUS-2 (BUS-B)</t>
+  </si>
+  <si>
+    <t>400KV_JP BINA</t>
+  </si>
+  <si>
+    <t>NON-OCCM-WR</t>
+  </si>
+  <si>
+    <t>PM of BUS-2 (BUS-B, BAY-1 &amp; BAY-5)</t>
+  </si>
+  <si>
+    <t>20-10-2026 09:00:00</t>
+  </si>
+  <si>
+    <t>31-10-2026 18:00:00</t>
+  </si>
+  <si>
+    <t>KRISHNA SINGH THAKUR</t>
+  </si>
+  <si>
+    <t>7987976012</t>
+  </si>
+  <si>
+    <t>MR2610/0675</t>
+  </si>
+  <si>
+    <t>132KV_132kv main bus no 2, 132kv IC Katni-1 line &amp; 160MVA BHEL X-MER</t>
+  </si>
+  <si>
+    <t>400KV_KATNI4</t>
+  </si>
+  <si>
+    <t>For replacement of main bus isolator</t>
+  </si>
+  <si>
+    <t>SK chaturvedi</t>
+  </si>
+  <si>
+    <t>9425806938</t>
+  </si>
+  <si>
+    <t>MR2610/0659</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA Transformer ECE Make</t>
+  </si>
+  <si>
+    <t>132KV_KHAJURAHO</t>
+  </si>
+  <si>
+    <t>Inspection of Oil Leakage Points and Gaskets of 40</t>
+  </si>
+  <si>
+    <t>27-10-2026 11:00:00</t>
   </si>
   <si>
     <t>Brajendra Soni</t>
@@ -148,192 +457,42 @@
     <t>9131327770</t>
   </si>
   <si>
-    <t>MR2610/0630</t>
-  </si>
-  <si>
-    <t>132KV_50 mva BHEL Xmer</t>
-  </si>
-  <si>
-    <t>220KV_CHICHLI</t>
-  </si>
-  <si>
-    <t>Post monsoon maintenance and testing</t>
-  </si>
-  <si>
-    <t>Hemendra malviya</t>
-  </si>
-  <si>
-    <t>9425804688</t>
-  </si>
-  <si>
-    <t>MR2610/0633</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Daloda DJ Energy-II</t>
-  </si>
-  <si>
-    <t>220KV_DALODA</t>
-  </si>
-  <si>
-    <t>for replacement of the TCH supervision relay</t>
-  </si>
-  <si>
-    <t>26-10-2026 13:00:00</t>
-  </si>
-  <si>
-    <t>26-10-2026 15:00:00</t>
-  </si>
-  <si>
-    <t>Shailendra Borasi</t>
-  </si>
-  <si>
-    <t>9907246485</t>
-  </si>
-  <si>
-    <t>MR2610/0635</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Daloda Renewable Energy</t>
-  </si>
-  <si>
-    <t>MR2610/0632</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Daloda DJ Energy-I</t>
-  </si>
-  <si>
-    <t>MR2610/0619</t>
-  </si>
-  <si>
-    <t>132KV_132kV Dindori Gorakhpur Line Ckt-I &amp; II Line</t>
-  </si>
-  <si>
-    <t>132KV_DINDORI</t>
-  </si>
-  <si>
-    <t>Hot Line OPGW Work &amp; Other Line Maintenance Work</t>
-  </si>
-  <si>
-    <t>25-10-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>05-11-2026 19:00:00</t>
-  </si>
-  <si>
-    <t>S.K. BHALADHARE</t>
-  </si>
-  <si>
-    <t>9425807264</t>
-  </si>
-  <si>
-    <t>MR2610/0614</t>
-  </si>
-  <si>
-    <t>50MVA_132/33KV_BBL_Xmer</t>
-  </si>
-  <si>
-    <t>220KV_GANJBASODA</t>
-  </si>
-  <si>
-    <t>TESTING WORK</t>
-  </si>
-  <si>
-    <t>220KV GANJ BASODA</t>
+    <t>MR2610/0668</t>
+  </si>
+  <si>
+    <t>40MVA_132/33KV_IMP_X'mer</t>
+  </si>
+  <si>
+    <t>132KV_KOTHIYA</t>
+  </si>
+  <si>
+    <t>PAINTING WORK</t>
+  </si>
+  <si>
+    <t>RAKESH SUMAN</t>
+  </si>
+  <si>
+    <t>7587951093</t>
+  </si>
+  <si>
+    <t>MR2610/0648</t>
+  </si>
+  <si>
+    <t>132KV_40MVA X-MER NO-1 MAKE IMP</t>
+  </si>
+  <si>
+    <t>132KV_LATERI</t>
+  </si>
+  <si>
+    <t>POST MANSOON MAINTENANCE &amp; TESTING WORK</t>
+  </si>
+  <si>
+    <t>MAHENDRA RAJ SAHU</t>
   </si>
   <si>
     <t>9425804982</t>
   </si>
   <si>
-    <t>MR2610/0639</t>
-  </si>
-  <si>
-    <t>132KV_63 MAV ABB TRANSFORMER</t>
-  </si>
-  <si>
-    <t>220KV_JABALPUR</t>
-  </si>
-  <si>
-    <t>TRANSFORMER PAINTING WORK</t>
-  </si>
-  <si>
-    <t>27-10-2026 17:00:00</t>
-  </si>
-  <si>
-    <t>SUNIL SHUKLA</t>
-  </si>
-  <si>
-    <t>7648817157</t>
-  </si>
-  <si>
-    <t>MR2609/0609</t>
-  </si>
-  <si>
-    <t>Continuous</t>
-  </si>
-  <si>
-    <t>400KV_400KV_400KV BUS-2 (BUS-B)</t>
-  </si>
-  <si>
-    <t>400KV_JP BINA</t>
-  </si>
-  <si>
-    <t>NON-OCCM-WR</t>
-  </si>
-  <si>
-    <t>PM of BUS-2 (BUS-B, BAY-1 &amp; BAY-5)</t>
-  </si>
-  <si>
-    <t>20-10-2026 09:00:00</t>
-  </si>
-  <si>
-    <t>31-10-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>KRISHNA SINGH THAKUR</t>
-  </si>
-  <si>
-    <t>7987976012</t>
-  </si>
-  <si>
-    <t>MR2610/0640</t>
-  </si>
-  <si>
-    <t>132KV_132kv main bus no 1 &amp; 132kv IC Katni-2 feeder</t>
-  </si>
-  <si>
-    <t>400KV_KATNI4</t>
-  </si>
-  <si>
-    <t>For conversion of main bujumpers 1z to 2z</t>
-  </si>
-  <si>
-    <t>26-10-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>SK chaturvedi</t>
-  </si>
-  <si>
-    <t>9425806938</t>
-  </si>
-  <si>
-    <t>MR2610/0636</t>
-  </si>
-  <si>
-    <t>132KV_40 MVA XMER</t>
-  </si>
-  <si>
-    <t>132KV_KOTHIYA</t>
-  </si>
-  <si>
-    <t>PAINTING WORK ON XMER.</t>
-  </si>
-  <si>
-    <t>RAKESH SUMAN</t>
-  </si>
-  <si>
-    <t>7587951093</t>
-  </si>
-  <si>
     <t>MR2609/0610</t>
   </si>
   <si>
@@ -355,127 +514,256 @@
     <t>9039761183</t>
   </si>
   <si>
-    <t>MR2610/0634</t>
-  </si>
-  <si>
-    <t>132KV_63 MVA BBL X-MER NO 1</t>
-  </si>
-  <si>
-    <t>132KV_MANSAKRA</t>
-  </si>
-  <si>
-    <t>POST MONSOON MAINTENANCE WORK</t>
+    <t>MR2610/0676</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA Xmer-1 Areva</t>
+  </si>
+  <si>
+    <t>220KV_MANDIDEEP</t>
+  </si>
+  <si>
+    <t>A.K. Verma</t>
+  </si>
+  <si>
+    <t>9425801324</t>
+  </si>
+  <si>
+    <t>MR2610/0466</t>
+  </si>
+  <si>
+    <t>132KV_132 kV Moondi - Kalisindh PH-1 &amp; PH-2 (NVDA) Line</t>
+  </si>
+  <si>
+    <t>132KV_MOONDI</t>
+  </si>
+  <si>
+    <t>For Tower Final Checking &amp; Stringing 2 ckt entire</t>
+  </si>
+  <si>
+    <t>17-10-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>Nitin Girdonia</t>
+  </si>
+  <si>
+    <t>9425804899</t>
+  </si>
+  <si>
+    <t>MR2610/0642</t>
+  </si>
+  <si>
+    <t>160MVA_220/132KV_BBL_X'mer</t>
+  </si>
+  <si>
+    <t>220KV_MORENA</t>
+  </si>
+  <si>
+    <t>Post monsoon maintenance &amp; testing work.</t>
+  </si>
+  <si>
+    <t>Amit kumar Dhaneliya</t>
+  </si>
+  <si>
+    <t>9425802242</t>
+  </si>
+  <si>
+    <t>MR2610/0677</t>
+  </si>
+  <si>
+    <t>132KV_132kV Nainpur Ghansour DCSS Radial Line</t>
+  </si>
+  <si>
+    <t>132KV_NAINPUR</t>
+  </si>
+  <si>
+    <t>MR2610/0641</t>
+  </si>
+  <si>
+    <t>132KV_132kV Nainpur Ghansour Line</t>
+  </si>
+  <si>
+    <t>OPGW replacement work</t>
+  </si>
+  <si>
+    <t>26-10-2026 07:00:00</t>
+  </si>
+  <si>
+    <t>MR2610/0669</t>
+  </si>
+  <si>
+    <t>132KV_132 KV Narsinghpur- Interconnector no -1</t>
+  </si>
+  <si>
+    <t>132KV_NARSINGHPUR1</t>
+  </si>
+  <si>
+    <t>Line isolator, Fly over jumper and CT replacment w</t>
+  </si>
+  <si>
+    <t>Jayprakash Dharne</t>
+  </si>
+  <si>
+    <t>7587951106</t>
+  </si>
+  <si>
+    <t>MR2610/0488</t>
+  </si>
+  <si>
+    <t>220KV_220 kV Panagar- Birsinghpur</t>
+  </si>
+  <si>
+    <t>220KV_PANAGAR</t>
+  </si>
+  <si>
+    <t>Jumper tightening by Contract basis</t>
+  </si>
+  <si>
+    <t>21-10-2026 08:00:00</t>
+  </si>
+  <si>
+    <t>Jitendra Tiwari</t>
+  </si>
+  <si>
+    <t>9425805298</t>
+  </si>
+  <si>
+    <t>MR2610/0674</t>
+  </si>
+  <si>
+    <t>132KV_40MVA XMER -2</t>
+  </si>
+  <si>
+    <t>132KV_REWA1</t>
+  </si>
+  <si>
+    <t>PMM</t>
+  </si>
+  <si>
+    <t>Kanishka Singh</t>
+  </si>
+  <si>
+    <t>9425804656</t>
+  </si>
+  <si>
+    <t>MR2610/0661</t>
+  </si>
+  <si>
+    <t>400KV_315MVA CGL-I Xmer</t>
+  </si>
+  <si>
+    <t>400KV_SAGAR</t>
+  </si>
+  <si>
+    <t>post monsoon maintenanace</t>
+  </si>
+  <si>
+    <t>27-10-2026 17:30:00</t>
+  </si>
+  <si>
+    <t>SrajanSisodiya</t>
+  </si>
+  <si>
+    <t>9425804341</t>
+  </si>
+  <si>
+    <t>MR2610/0672</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA BHEL XMER AT 132 KV SLEEMNABAD</t>
+  </si>
+  <si>
+    <t>132KV_SALEEMNABAD</t>
+  </si>
+  <si>
+    <t>POST MONSOON MAINTENANCE</t>
   </si>
   <si>
     <t>R P RAWAT</t>
   </si>
   <si>
-    <t>9909030507</t>
-  </si>
-  <si>
-    <t>MR2610/0466</t>
-  </si>
-  <si>
-    <t>132KV_132 kV Moondi - Kalisindh PH-1 &amp; PH-2 (NVDA) Line</t>
-  </si>
-  <si>
-    <t>132KV_MOONDI</t>
-  </si>
-  <si>
-    <t>For Tower Final Checking &amp; Stringing 2 ckt entire</t>
-  </si>
-  <si>
-    <t>17-10-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>Nitin Girdonia</t>
-  </si>
-  <si>
-    <t>9425804899</t>
-  </si>
-  <si>
-    <t>MR2610/0641</t>
-  </si>
-  <si>
-    <t>132KV_132kV Nainpur Ghansour Line</t>
-  </si>
-  <si>
-    <t>132KV_NAINPUR</t>
-  </si>
-  <si>
-    <t>OPGW replacement work</t>
-  </si>
-  <si>
-    <t>26-10-2026 07:00:00</t>
-  </si>
-  <si>
-    <t>Amol Shende</t>
-  </si>
-  <si>
-    <t>7587951136</t>
-  </si>
-  <si>
-    <t>MR2610/0615</t>
-  </si>
-  <si>
-    <t>132KV_132 KV NARSINGHPUR- INTERCONNECTOR NO.II</t>
-  </si>
-  <si>
-    <t>220KV_NARSINGHPUR</t>
-  </si>
-  <si>
-    <t>CONDUCTOR REPLACEMENT WORK BY APAR  INDUSTRIE</t>
-  </si>
-  <si>
-    <t>25-10-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>DINESH KUSHWAHA</t>
-  </si>
-  <si>
-    <t>9425182413</t>
-  </si>
-  <si>
-    <t>MR2610/0488</t>
-  </si>
-  <si>
-    <t>220KV_220 kV Panagar- Birsinghpur</t>
-  </si>
-  <si>
-    <t>220KV_PANAGAR</t>
-  </si>
-  <si>
-    <t>Jumper tightening by Contract basis</t>
-  </si>
-  <si>
-    <t>21-10-2026 08:00:00</t>
-  </si>
-  <si>
-    <t>28-10-2026 18:00:00</t>
-  </si>
-  <si>
-    <t>Jitendra Tiwari</t>
-  </si>
-  <si>
-    <t>9425805298</t>
-  </si>
-  <si>
-    <t>MR2610/0611</t>
-  </si>
-  <si>
-    <t>220KV_ITARSI-PIPARIYA_Ckt_2</t>
-  </si>
-  <si>
-    <t>220KV_PIPARIYA</t>
-  </si>
-  <si>
-    <t>Penal Replacement Work at 220 kv ss Pipariya</t>
-  </si>
-  <si>
-    <t>S.K.dehariya</t>
-  </si>
-  <si>
-    <t>8319638787</t>
+    <t>9907030507</t>
+  </si>
+  <si>
+    <t>MR2610/0673</t>
+  </si>
+  <si>
+    <t>132KV_132kv 63mva xmer make bbl</t>
+  </si>
+  <si>
+    <t>220KV_SATNA</t>
+  </si>
+  <si>
+    <t>For postmansoon and testing work</t>
+  </si>
+  <si>
+    <t>Poshkar kushwaha</t>
+  </si>
+  <si>
+    <t>9425813990</t>
+  </si>
+  <si>
+    <t>MR2610/0645</t>
+  </si>
+  <si>
+    <t>132KV_50 MVA X-MER (BHEL)</t>
+  </si>
+  <si>
+    <t>220KV_SEONI</t>
+  </si>
+  <si>
+    <t>33 KV Main Bus Shutdown</t>
+  </si>
+  <si>
+    <t>Arshad Qureshi</t>
+  </si>
+  <si>
+    <t>7648817144</t>
+  </si>
+  <si>
+    <t>MR2610/0644</t>
+  </si>
+  <si>
+    <t>132KV_40 MVA X-MER (BBL)</t>
+  </si>
+  <si>
+    <t>MR2610/0670</t>
+  </si>
+  <si>
+    <t>132KV_132kv Shivpuri Mohna Ckt-1</t>
+  </si>
+  <si>
+    <t>220KV_SHIVPURI</t>
+  </si>
+  <si>
+    <t>Line Maintenance work</t>
+  </si>
+  <si>
+    <t>Suraj pawar</t>
+  </si>
+  <si>
+    <t>9425814079</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA XMER BHEL</t>
+  </si>
+  <si>
+    <t>220KV_SIDHI</t>
+  </si>
+  <si>
+    <t>CT DGA OIL SAMPLING TAKEN BY SERVICE ENGINEERR  OF</t>
+  </si>
+  <si>
+    <t>27-10-2026 12:00:00</t>
+  </si>
+  <si>
+    <t>Er VIJAY OJHA</t>
+  </si>
+  <si>
+    <t>9755836908</t>
+  </si>
+  <si>
+    <t>MR2610/0655</t>
   </si>
   <si>
     <t>MR2610/0568</t>
@@ -499,94 +787,130 @@
     <t>9425806398</t>
   </si>
   <si>
-    <t>MR2610/0482</t>
-  </si>
-  <si>
-    <t>220KV_160 mva 2nd bbl-make Transformer</t>
-  </si>
-  <si>
-    <t>Oil leakage attend from bell-tank</t>
-  </si>
-  <si>
-    <t>22-10-2026 10:00:00</t>
-  </si>
-  <si>
     <t>31-10-2026 17:00:00</t>
   </si>
   <si>
-    <t>MR2610/0613</t>
-  </si>
-  <si>
-    <t>220KV_220 KV Chichli-Udaipura I</t>
-  </si>
-  <si>
-    <t>220KV_UDAIPURA</t>
-  </si>
-  <si>
-    <t>DISC REPLACEMENT WORK</t>
-  </si>
-  <si>
-    <t>Ashutosh Rai</t>
-  </si>
-  <si>
-    <t>9425806902</t>
+    <t>MR2610/0460</t>
+  </si>
+  <si>
+    <t>220KV_160 MVA 2nd bbl-make Transformer</t>
+  </si>
+  <si>
+    <t>Oil leakage attend from bell-Tank</t>
+  </si>
+  <si>
+    <t>21-10-2026 10:00:00</t>
+  </si>
+  <si>
+    <t>Pushpendra soni</t>
   </si>
   <si>
     <t>ok</t>
   </si>
   <si>
+    <t>o&amp;m consent required</t>
+  </si>
+  <si>
+    <t>sub ld</t>
+  </si>
+  <si>
     <t>ok, line to be in service</t>
   </si>
   <si>
-    <t>sub ld</t>
-  </si>
-  <si>
-    <t>approved on daily basis</t>
+    <t>RTS consent required</t>
+  </si>
+  <si>
+    <t>real time</t>
   </si>
   <si>
     <t>ok, through sub ld</t>
   </si>
   <si>
-    <t>ok, through sub ld, line to be in service through TBC. RE plant to inform</t>
-  </si>
-  <si>
-    <t>deferred by site</t>
-  </si>
-  <si>
-    <t>400KV-JABALPUR-ITARSI-2</t>
+    <t>work done</t>
+  </si>
+  <si>
+    <t>NOT APPROVED FOR 27TH DUE TO NHPTL TESTING</t>
+  </si>
+  <si>
+    <t>real time, as per loading conditions</t>
+  </si>
+  <si>
+    <t>APPROVED OUTAGE LIST FOR DATED 27.10.2026</t>
+  </si>
+  <si>
+    <t>400KV-NAGDA-SHUJALPUR-2</t>
   </si>
   <si>
     <t>POWERGRID-WR2 (PGCIL)</t>
   </si>
   <si>
-    <t>Sensitivity of tripping 400KV-JABALPUR-ITARSI-2 is 12% on 400KV-JABALPUR-ITARSI-4. All other lines at JABALPUR - 400KV and ITARSI - 400KV to be in service. SLDC MP to be informed.</t>
-  </si>
-  <si>
-    <t>WR OCCM</t>
-  </si>
-  <si>
-    <t>BHOPAL-MP - 400KV - BUS 1</t>
-  </si>
-  <si>
-    <t>for alignment of Bus-1 PG Isolator, simultaneously 400KV-BHOPAL-MP-SAGAR-1 Outage required</t>
-  </si>
-  <si>
-    <t>Deferred  because the tie CB of 400kV Bhopal-Bina 2 and main CB of 400kv Bhopal-BDTCL  2 are out.</t>
-  </si>
-  <si>
-    <t>400KV-NAGDA-SHUJALPUR-1</t>
-  </si>
-  <si>
-    <t>Attending S/D nature defect in line . Dia to be kept open at both ends.</t>
-  </si>
-  <si>
-    <t>132KV-KIRNAPUR-DONGARGARH-1</t>
-  </si>
-  <si>
-    <t>Tree Cutting work at between loc. 286-294</t>
-  </si>
-  <si>
-    <t>CG SLDC</t>
+    <t>27-Oct-2026</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outage for Nature defect attending work from Shujalpur TLM </t>
+  </si>
+  <si>
+    <t>BHOPAL-MP - 400KV - BUS 2</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>Simultaneous outage of BHOPAL-MP - 400KV - BUS 2 and 400KV-BHOPAL-MP-DAMOH-1 is required for Damoh-1 Main Bay LBB Ratrofitting work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deferred  </t>
+  </si>
+  <si>
+    <t>400KV-DAMOH-KATNI-1</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>220KV-DAMOH-DAMOH-MP-1</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS &amp; FOR BAY MAINTENANCE &amp; TESTING WORK AT SUBSTASTION, REPLACEMENT OF DAMAGED CLAMPS/JUMPERS ETC.</t>
+  </si>
+  <si>
+    <t>220KV-GWALIOR-DATIA-1</t>
+  </si>
+  <si>
+    <t>220KV-PANDURNA-KALMESHWAR-1</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH,MAHARASHTRA</t>
+  </si>
+  <si>
+    <t>FOR LINE MAINTENANCE WORK I.E. CLEANING OF DISC INSULATORS DURING LINE PATROLLING, REPLACEMENT OF FLASHOVERED DISC INSULATORS, TREE BRANCH CUTTING ETC AT VARIOUS TOWER LOCATIONS</t>
+  </si>
+  <si>
+    <t>220KV-ANNUPUR-KOTMIKALA-2</t>
+  </si>
+  <si>
+    <t>MADHYA PRADESH,CHATTISGARH</t>
+  </si>
+  <si>
+    <t>220KV-INDORE-INDORE NORTH ZONE-2</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>220KV-SHUJALPUR-RAJGARH-MP-2</t>
   </si>
   <si>
     <t>JP-BINA - 400KV - BUS 2</t>
@@ -595,10 +919,34 @@
     <t>JP BINA</t>
   </si>
   <si>
+    <t>20-Oct-2026</t>
+  </si>
+  <si>
+    <t>31-Oct-2026</t>
+  </si>
+  <si>
     <t>For overhauling, maintenance &amp; testing of the Pantograph &amp; HCB Isolators (R, Y &amp; B Phases)</t>
   </si>
   <si>
-    <t>approved on daily basis by WRLDC</t>
+    <t>DEFERRED FOR 27TH DUE TO NHPTL TESTING</t>
+  </si>
+  <si>
+    <t>NHPTL-TESTING-@-NHPTL - 400KV at BINA-NHPTL - 400KV</t>
+  </si>
+  <si>
+    <t>NHPTL</t>
+  </si>
+  <si>
+    <t>17:59</t>
+  </si>
+  <si>
+    <t>SC testing</t>
+  </si>
+  <si>
+    <t>JP BINA CONSENT PENDING</t>
+  </si>
+  <si>
+    <t>S/I SLDC JABALPUR</t>
   </si>
 </sst>
 </file>
@@ -609,10 +957,17 @@
     <numFmt numFmtId="164" formatCode="[$-1010809]dd\-mm\-yyyy"/>
     <numFmt numFmtId="165" formatCode="[$-1010809]dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -643,13 +998,34 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -667,36 +1043,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -724,17 +1082,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -780,13 +1127,35 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -795,101 +1164,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -924,7 +1275,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -967,7 +1324,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -979,7 +1336,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -1026,6 +1383,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -1061,6 +1435,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1213,57 +1604,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.140625" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="49.85546875" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="49.42578125" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="53.28515625" customWidth="1"/>
     <col min="9" max="10" width="19.5703125" customWidth="1"/>
-    <col min="11" max="11" width="25.42578125" customWidth="1"/>
+    <col min="11" max="11" width="24.42578125" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="45.140625" style="16" customWidth="1"/>
+    <col min="13" max="13" width="54.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="43.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="12"/>
     </row>
     <row r="2" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="E2" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="16"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="13"/>
+      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -1286,7 +1678,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="13"/>
+      <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
@@ -1319,15 +1711,15 @@
       <c r="J4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="14" t="s">
+      <c r="L4" s="12"/>
+      <c r="M4" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -1364,17 +1756,16 @@
       <c r="L5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <f>A5+1</f>
         <v>2</v>
       </c>
       <c r="B6" s="5">
-        <v>46320.628541666665</v>
+        <v>46321.530624999999</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>27</v>
@@ -1404,17 +1795,16 @@
       <c r="L6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <f t="shared" ref="A7:A32" si="0">A6+1</f>
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>46320.436851851853</v>
+        <v>46321.611504629633</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>35</v>
@@ -1424,16 +1814,16 @@
         <v>36</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>32</v>
@@ -1444,17 +1834,16 @@
       <c r="L7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="M7" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>46320.474456018521</v>
+        <v>46321.536145833335</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>41</v>
@@ -1473,38 +1862,37 @@
         <v>44</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>46320.564571759256</v>
+        <v>46321.588969907411</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>21</v>
@@ -1516,919 +1904,1725 @@
         <v>51</v>
       </c>
       <c r="J9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="L9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="L9" s="8" t="s">
+      <c r="M9" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>46321.600787037038</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B10" s="5">
-        <v>46320.565740740742</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="5">
-        <v>46320.563321759262</v>
+        <v>46319.629733796297</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="E11" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="M11" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="5">
-        <v>46319.629733796297</v>
+        <v>46321.611608796295</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="4" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="5">
-        <v>46319.56449074074</v>
+        <v>46321.612175925926</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="5">
-        <v>46320.642534722225</v>
+        <v>46321.722557870373</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="M14" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="5">
-        <v>46294.889849537038</v>
+        <v>46321.569201388891</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>81</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D15" s="4"/>
       <c r="E15" s="4" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="M15" s="15" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="5">
-        <v>46320.655613425923</v>
+        <v>46321.575185185182</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>31</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="5">
-        <v>46320.615763888891</v>
+        <v>46321.533090277779</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>32</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="M17" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="5">
-        <v>46295.47079861111</v>
+        <v>46317.636921296296</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="M18" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="5">
-        <v>46320.565555555557</v>
+        <v>46321.756712962961</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D19" s="4"/>
-      <c r="E19" s="4" t="s">
-        <v>111</v>
+      <c r="E19" s="9" t="s">
+        <v>117</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="M19" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46311.720057870371</v>
+        <v>46294.889849537038</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="M20" s="15" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="5">
-        <v>46320.696435185186</v>
+        <v>46321.679907407408</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="D21" s="4"/>
       <c r="E21" s="4" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>127</v>
+        <v>31</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="M21" s="15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="5">
-        <v>46319.597291666665</v>
+        <v>46321.580636574072</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>81</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="D22" s="4"/>
       <c r="E22" s="4" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G22" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="M22" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="M22" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="5">
-        <v>46315.461215277777</v>
+        <v>46321.622291666667</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="D23" s="4"/>
       <c r="E23" s="4" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G23" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>141</v>
+        <v>51</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="M23" s="15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="M23" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="5">
-        <v>46319.502141203702</v>
+        <v>46321.529872685183</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G24" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>31</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="M24" s="15" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
-        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B25" s="5">
-        <v>46317.605763888889</v>
+        <v>46295.47079861111</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="M25" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
-        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" s="5">
-        <v>46314.580069444448</v>
+        <v>46321.684965277775</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>81</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>161</v>
+        <v>31</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="M26" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
-        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B27" s="20">
-        <v>46319.508055555554</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="G27" s="21" t="s">
+      <c r="B27" s="5">
+        <v>46311.720057870371</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="M27" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5">
+        <v>46321.454629629632</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="I27" s="22" t="s">
+      <c r="H28" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5">
+        <v>46321.699849537035</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46320.696435185186</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5">
+        <v>46321.629502314812</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="M31" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>28</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46315.461215277777</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>29</v>
+      </c>
+      <c r="B33" s="5">
+        <v>46321.655370370368</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="22" t="s">
+      <c r="J33" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M33" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>30</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46321.586215277777</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>31</v>
+      </c>
+      <c r="B35" s="5">
+        <v>46321.645833333336</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="K27" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="L27" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="M27" s="25" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="G28" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="I28" s="27" t="s">
+      <c r="K35" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>32</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46321.646990740737</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J28" s="27">
-        <v>46321.541666666664</v>
-      </c>
-      <c r="K28" s="17"/>
-      <c r="L28" s="17"/>
-      <c r="M28" s="17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="23">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="F29" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="G29" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="H29" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="I29" s="33" t="s">
+      <c r="J36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="M36" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>33</v>
+      </c>
+      <c r="B37" s="5">
+        <v>46321.488599537035</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>34</v>
+      </c>
+      <c r="B38" s="5">
+        <v>46321.484560185185</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>35</v>
+      </c>
+      <c r="B39" s="5">
+        <v>46321.644155092596</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I39" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="J29" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="34" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="G30" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="I30" s="27">
-        <v>46321.333333333336</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="K30" s="17"/>
-      <c r="L30" s="17"/>
-      <c r="M30" s="29" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" s="26"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="I31" s="27">
-        <v>46321.333333333336</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="K31" s="17"/>
-      <c r="L31" s="17"/>
-      <c r="M31" s="35" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="E32" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="G32" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="I32" s="27">
-        <v>46321.333333333336</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="19" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="33" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="J39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>36</v>
+      </c>
+      <c r="B40" s="5">
+        <v>46321.573078703703</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4">
+        <v>37</v>
+      </c>
+      <c r="B41" s="5">
+        <v>46317.605763888889</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4">
+        <v>38</v>
+      </c>
+      <c r="B42" s="18">
+        <v>46311.65284722222</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="G42" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="I42" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="J42" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="L42" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="M42" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="4">
+        <v>39</v>
+      </c>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="G43" s="22"/>
+      <c r="H43" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="J43" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="K43" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="L43" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="M43" s="24" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="4">
+        <v>40</v>
+      </c>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="G44" s="22"/>
+      <c r="H44" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="I44" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J44" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="K44" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L44" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="M44" s="25" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>41</v>
+      </c>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="F45" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="G45" s="22"/>
+      <c r="H45" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="I45" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J45" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="K45" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L45" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="M45" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>42</v>
+      </c>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="G46" s="22"/>
+      <c r="H46" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="I46" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J46" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="K46" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L46" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="M46" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="4">
+        <v>43</v>
+      </c>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="F47" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="G47" s="22"/>
+      <c r="H47" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="I47" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J47" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="K47" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L47" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="M47" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
+        <v>44</v>
+      </c>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="F48" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="G48" s="22"/>
+      <c r="H48" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="I48" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J48" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="K48" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L48" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="M48" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A49" s="4">
+        <v>45</v>
+      </c>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="F49" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="G49" s="22"/>
+      <c r="H49" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="I49" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J49" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="K49" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L49" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="M49" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A50" s="4">
+        <v>46</v>
+      </c>
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="G50" s="22"/>
+      <c r="H50" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="I50" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J50" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="K50" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L50" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="M50" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="A51" s="4">
+        <v>47</v>
+      </c>
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="F51" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="G51" s="22"/>
+      <c r="H51" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="I51" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J51" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="K51" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L51" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="M51" s="26" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="4">
+        <v>48</v>
+      </c>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="F52" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="G52" s="22"/>
+      <c r="H52" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="I52" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="J52" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="K52" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="L52" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="M52" s="26" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="4">
+        <v>49</v>
+      </c>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="F53" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="G53" s="22"/>
+      <c r="H53" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="I53" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="J53" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="K53" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="L53" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="M53" s="26" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="22"/>
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="22"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="22"/>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="27" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="22"/>
+      <c r="M55" s="22"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:M1"/>
     <mergeCell ref="K4:L4"/>
+    <mergeCell ref="E2:J2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>
